--- a/Analysis Examples/Transaction-Details-Analysis.xlsx
+++ b/Analysis Examples/Transaction-Details-Analysis.xlsx
@@ -6,11 +6,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RR Analysis" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analysis" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transaction Details" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Transaction Details'!$A$2:$AC$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Analysis'!$A$1:$R$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Transaction Details'!$A$2:$AC$53</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="29">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -95,8 +96,100 @@
       <color rgb="FF000000"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="008B0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="008B0000"/>
+      <sz val="32"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="008B0000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="006B3A00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="004A3B00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -168,6 +261,60 @@
         <fgColor rgb="FF1F3864"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+        <bgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+        <bgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0E0"/>
+        <bgColor rgb="00FFE0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+        <bgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF0DC"/>
+        <bgColor rgb="00FFF0DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEFBD8"/>
+        <bgColor rgb="00FEFBD8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5DEB3"/>
+        <bgColor rgb="00F5DEB3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -214,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -381,6 +528,73 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -469,7 +683,7 @@
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -510,16 +724,9 @@
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr algn="l">
-            <a:spcBef>
-              <a:spcPts val="400"/>
-            </a:spcBef>
-          </a:pPr>
+          <a:pPr algn="l"/>
           <a:r>
             <a:rPr lang="en-US" sz="1200" b="0" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
               <a:latin typeface="Arial"/>
             </a:rPr>
             <a:t> </a:t>
@@ -550,20 +757,13 @@
               </a:solidFill>
               <a:latin typeface="Arial"/>
             </a:rPr>
-            <a:t>The Transaction Detail report shows every individual cardex and GL entry for a specific document — sales order, work order, purchase order, or adjustment. It is the deepest drill-down available for investigating a reconciliation variance. This compares the item ledger F4111 to GL details F0911.</a:t>
+            <a:t>The Transaction Detail report shows every cardex and GL entry for a single document. It is the deepest drill-down available for investigating a reconciliation variance, comparing the item ledger F4111 to GL details F0911.</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr algn="l">
-            <a:spcBef>
-              <a:spcPts val="400"/>
-            </a:spcBef>
-          </a:pPr>
+          <a:pPr algn="l"/>
           <a:r>
             <a:rPr lang="en-US" sz="1200" b="0" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
               <a:latin typeface="Arial"/>
             </a:rPr>
             <a:t> </a:t>
@@ -594,20 +794,13 @@
               </a:solidFill>
               <a:latin typeface="Arial"/>
             </a:rPr>
-            <a:t>When a transaction variance appears in RapidReconciler, the root cause is always in a specific transaction. This report exposes the exact cardex row, GL entry, and DMAAI configuration responsible.</a:t>
+            <a:t>When a transaction variance appears in RapidReconciler the root cause is always in a specific transaction. This report exposes the exact cardex row, GL entry, and DMAAI configuration responsible.</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr algn="l">
-            <a:spcBef>
-              <a:spcPts val="400"/>
-            </a:spcBef>
-          </a:pPr>
+          <a:pPr algn="l"/>
           <a:r>
             <a:rPr lang="en-US" sz="1200" b="0" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
               <a:latin typeface="Arial"/>
             </a:rPr>
             <a:t> </a:t>
@@ -638,20 +831,13 @@
               </a:solidFill>
               <a:latin typeface="Arial"/>
             </a:rPr>
-            <a:t>This analysis traces a single document through the cardex and GL, identifies the mismatch, confirms the expected vs. actual account posting, and provides the specific journal entry required to correct it.</a:t>
+            <a:t>This analysis traces a single document through the cardex and GL, identifies the mismatch, confirms expected vs. actual posting, and provides the journal entry required to correct it.</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr algn="l">
-            <a:spcBef>
-              <a:spcPts val="400"/>
-            </a:spcBef>
-          </a:pPr>
+          <a:pPr algn="l"/>
           <a:r>
             <a:rPr lang="en-US" sz="1200" b="0" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
               <a:latin typeface="Arial"/>
             </a:rPr>
             <a:t> </a:t>
@@ -682,7 +868,7 @@
               </a:solidFill>
               <a:latin typeface="Arial"/>
             </a:rPr>
-            <a:t>RR Analysis = findings and recommended actions. Transaction Details = source export data.</a:t>
+            <a:t>Analysis sheet = findings and actions.   Transaction Details sheet = source export data.   Click any "Row N" link in the Evidence section to jump to that row.</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1011,778 +1197,297 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" style="30" min="1" max="1"/>
-    <col width="52" customWidth="1" style="30" min="2" max="2"/>
-    <col width="20" customWidth="1" style="30" min="3" max="4"/>
-    <col width="16" customWidth="1" style="30" min="4" max="4"/>
-    <col width="8" customWidth="1" style="30" min="6" max="6"/>
+    <col width="24" customWidth="1" style="30" min="1" max="1"/>
+    <col width="30" customWidth="1" style="30" min="2" max="2"/>
+    <col width="38" customWidth="1" style="30" min="3" max="3"/>
+    <col width="22" customWidth="1" style="30" min="4" max="4"/>
+    <col width="22" customWidth="1" style="30" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" s="30">
-      <c r="A1" s="51" t="inlineStr">
-        <is>
-          <t>RapidReconciler Transaction Analysis</t>
-        </is>
-      </c>
-      <c r="F1" s="59" t="n"/>
-    </row>
-    <row r="2" s="30">
-      <c r="A2" s="39" t="inlineStr">
-        <is>
-          <t>Document DOC-00001 (RI)  ·  Company 00010  ·  Sales Order ORD-00001 (SO)</t>
-        </is>
-      </c>
-      <c r="F2" s="60" t="n"/>
-    </row>
-    <row r="3" s="30">
-      <c r="A3" s="38" t="n"/>
-      <c r="B3" s="38" t="n"/>
-      <c r="C3" s="38" t="n"/>
-      <c r="D3" s="38" t="n"/>
-      <c r="F3" s="61" t="n"/>
-    </row>
-    <row r="4" ht="42" customHeight="1" s="30">
-      <c r="A4" s="52" t="inlineStr">
-        <is>
-          <t>1 · Document</t>
-        </is>
-      </c>
-      <c r="B4" s="53" t="n"/>
-      <c r="C4" s="53" t="n"/>
-      <c r="D4" s="53" t="n"/>
-      <c r="F4" s="60" t="n"/>
-    </row>
-    <row r="5" s="30">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>Document Number</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>DOC-00001</t>
-        </is>
-      </c>
-      <c r="C5" s="42" t="n"/>
-      <c r="D5" s="42" t="n"/>
-      <c r="F5" s="60" t="n"/>
-    </row>
-    <row r="6" s="30">
-      <c r="A6" s="24" t="inlineStr">
-        <is>
-          <t>Document Type</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>RI — Sales Invoice / Shipment</t>
-        </is>
-      </c>
-      <c r="C6" s="43" t="n"/>
-      <c r="D6" s="43" t="n"/>
-      <c r="F6" s="61" t="n"/>
-    </row>
-    <row r="7" ht="42" customHeight="1" s="30">
-      <c r="A7" s="22" t="inlineStr">
-        <is>
-          <t>Order Number</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>ORD-00001</t>
-        </is>
-      </c>
-      <c r="C7" s="42" t="n"/>
-      <c r="D7" s="42" t="n"/>
-      <c r="F7" s="60" t="n"/>
-    </row>
-    <row r="8" s="30">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>Order Type</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>SO — Sales Order</t>
-        </is>
-      </c>
-      <c r="C8" s="43" t="n"/>
-      <c r="D8" s="43" t="n"/>
-      <c r="F8" s="60" t="n"/>
-    </row>
-    <row r="9" s="30">
-      <c r="A9" s="22" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>00010</t>
-        </is>
-      </c>
-      <c r="C9" s="42" t="n"/>
-      <c r="D9" s="42" t="n"/>
-      <c r="F9" s="61" t="n"/>
-    </row>
-    <row r="10" ht="42" customHeight="1" s="30">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>April 20, 2026  (transaction activity dates from August 2016)</t>
-        </is>
-      </c>
-      <c r="C10" s="43" t="n"/>
-      <c r="D10" s="43" t="n"/>
-      <c r="F10" s="60" t="n"/>
-    </row>
-    <row r="11" s="30">
-      <c r="A11" s="22" t="inlineStr">
-        <is>
-          <t>Variance Amount</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>$338.00  (GL credit with no cardex offset)</t>
-        </is>
-      </c>
-      <c r="C11" s="42" t="n"/>
-      <c r="D11" s="42" t="n"/>
-      <c r="F11" s="60" t="n"/>
-    </row>
-    <row r="12" s="30">
-      <c r="A12" s="38" t="n"/>
-      <c r="B12" s="38" t="n"/>
-      <c r="C12" s="38" t="n"/>
-      <c r="D12" s="38" t="n"/>
-      <c r="F12" s="61" t="n"/>
-    </row>
-    <row r="13" ht="42" customHeight="1" s="30">
-      <c r="A13" s="52" t="inlineStr">
-        <is>
-          <t>2 · Unassigned Check</t>
-        </is>
-      </c>
-      <c r="B13" s="53" t="n"/>
-      <c r="C13" s="53" t="n"/>
-      <c r="D13" s="53" t="n"/>
-      <c r="F13" s="60" t="n"/>
-    </row>
-    <row r="14" s="30">
-      <c r="A14" s="22" t="inlineStr">
-        <is>
-          <t>Unassigned Section Present?</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>No — no Unassigned section found in the report</t>
-        </is>
-      </c>
-      <c r="C14" s="42" t="n"/>
-      <c r="D14" s="42" t="n"/>
-    </row>
-    <row r="15" ht="28" customHeight="1" s="30">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>F4111 Total Understated?</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>No — F4111 Total of $0.00 reflects the complete cardex for this document</t>
-        </is>
-      </c>
-      <c r="C15" s="43" t="n"/>
-      <c r="D15" s="43" t="n"/>
-    </row>
-    <row r="16" ht="28" customHeight="1" s="30">
-      <c r="A16" s="22" t="inlineStr">
-        <is>
-          <t>True Cardex Total</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>$0.00  (no cardex entries exist for document DOC-00001 RI)</t>
-        </is>
-      </c>
-      <c r="C16" s="42" t="n"/>
-      <c r="D16" s="42" t="n"/>
-    </row>
-    <row r="17" ht="16" customHeight="1" s="30">
-      <c r="A17" s="38" t="n"/>
-      <c r="B17" s="38" t="n"/>
-      <c r="C17" s="38" t="n"/>
-      <c r="D17" s="38" t="n"/>
-    </row>
-    <row r="18" ht="16" customHeight="1" s="30">
-      <c r="A18" s="52" t="inlineStr">
-        <is>
-          <t>3 · RR Summary Findings</t>
-        </is>
-      </c>
-      <c r="B18" s="53" t="n"/>
-      <c r="C18" s="53" t="n"/>
-      <c r="D18" s="53" t="n"/>
-    </row>
-    <row r="19" ht="16" customHeight="1" s="30">
-      <c r="A19" s="44" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B19" s="44" t="inlineStr">
-        <is>
-          <t>Cardex (F4111)</t>
-        </is>
-      </c>
-      <c r="C19" s="44" t="inlineStr">
-        <is>
-          <t>GL (F0911)</t>
-        </is>
-      </c>
-      <c r="D19" s="44" t="inlineStr">
-        <is>
-          <t>Variance</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1" s="30">
-      <c r="A20" s="45" t="inlineStr">
-        <is>
-          <t>F4111 Total</t>
-        </is>
-      </c>
-      <c r="B20" s="45" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="C20" s="45" t="n"/>
-      <c r="D20" s="45" t="n"/>
-    </row>
-    <row r="21" ht="16" customHeight="1" s="30">
-      <c r="A21" s="46" t="inlineStr">
-        <is>
-          <t>F0911 Total</t>
-        </is>
-      </c>
-      <c r="B21" s="46" t="n"/>
-      <c r="C21" s="46" t="inlineStr">
-        <is>
-          <t>($338.00)</t>
-        </is>
-      </c>
-      <c r="D21" s="46" t="n"/>
-    </row>
-    <row r="22" ht="16" customHeight="1" s="30">
-      <c r="A22" s="47" t="inlineStr">
-        <is>
-          <t>RR Net</t>
-        </is>
-      </c>
-      <c r="B22" s="47" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="C22" s="47" t="inlineStr">
-        <is>
-          <t>($338.00)</t>
-        </is>
-      </c>
-      <c r="D22" s="47" t="inlineStr">
+    <row r="1" ht="6" customHeight="1" s="30">
+      <c r="A1" s="62" t="n"/>
+      <c r="B1" s="62" t="n"/>
+      <c r="C1" s="62" t="n"/>
+      <c r="D1" s="62" t="n"/>
+      <c r="E1" s="62" t="n"/>
+    </row>
+    <row r="2" ht="38" customHeight="1" s="30">
+      <c r="A2" s="63" t="inlineStr">
+        <is>
+          <t>Document DOC-00001 (RI Sales Invoice) — Order ORD-00001 (SO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" s="30">
+      <c r="A3" s="64" t="inlineStr">
+        <is>
+          <t>GL credit of $338.00 has no inventory match</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="30">
+      <c r="A4" s="65" t="inlineStr">
+        <is>
+          <t>Company  00010          GL Date  Aug 11 2016          Period  Apr 20 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="10" customHeight="1" s="30"/>
+    <row r="6" ht="20" customHeight="1" s="30">
+      <c r="A6" s="66" t="inlineStr">
+        <is>
+          <t>VARIANCE  (Priority 1 — investigate immediately)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1" s="30">
+      <c r="A7" s="67" t="inlineStr">
         <is>
           <t>$338.00</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="16" customHeight="1" s="30">
-      <c r="A23" s="38" t="n"/>
-      <c r="B23" s="38" t="n"/>
-      <c r="C23" s="38" t="n"/>
-      <c r="D23" s="38" t="n"/>
-    </row>
-    <row r="24" ht="42" customHeight="1" s="30">
-      <c r="A24" s="22" t="inlineStr">
-        <is>
-          <t>Pattern Classification</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>GL-Only Entry — inventory account has a credit of ($338.00) with no corresponding cardex record (F4111 is completely empty for this document)</t>
-        </is>
-      </c>
-      <c r="C24" s="42" t="n"/>
-      <c r="D24" s="42" t="n"/>
-    </row>
-    <row r="25" ht="16" customHeight="1" s="30">
-      <c r="A25" s="38" t="n"/>
-      <c r="B25" s="38" t="n"/>
-      <c r="C25" s="38" t="n"/>
-      <c r="D25" s="38" t="n"/>
-    </row>
-    <row r="26" ht="16" customHeight="1" s="30">
-      <c r="A26" s="52" t="inlineStr">
-        <is>
-          <t>4 · Root Cause</t>
-        </is>
-      </c>
-      <c r="B26" s="53" t="n"/>
-      <c r="C26" s="53" t="n"/>
-      <c r="D26" s="53" t="n"/>
-    </row>
-    <row r="27" ht="28" customHeight="1" s="30">
-      <c r="A27" s="22" t="inlineStr">
-        <is>
-          <t>Pattern (Section 4 Ref)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Section 4: Non-Stock Line Posted to Inventory Account</t>
-        </is>
-      </c>
-      <c r="C27" s="42" t="n"/>
-      <c r="D27" s="42" t="n"/>
-    </row>
-    <row r="28" ht="28" customHeight="1" s="30">
-      <c r="A28" s="24" t="inlineStr">
-        <is>
-          <t>GL Entry</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Account BU1.142000  ·  GL Class BUYP  ·  Batch BATCH-00001 IB  ·  Amount ($338.00)</t>
-        </is>
-      </c>
-      <c r="C28" s="43" t="n"/>
-      <c r="D28" s="43" t="n"/>
-    </row>
-    <row r="29" ht="28" customHeight="1" s="30">
-      <c r="A29" s="28" t="inlineStr">
-        <is>
-          <t>F0911 Comment (explicit)</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>"Non stock line in Inv acct" — RapidReconciler identified the root cause in the Comment field</t>
-        </is>
-      </c>
-      <c r="C29" s="48" t="n"/>
-      <c r="D29" s="48" t="n"/>
-    </row>
-    <row r="30" ht="28" customHeight="1" s="30">
-      <c r="A30" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>ITEM-00004  (item ITEM-00004 — 1,000 EA @ $0.338 = $338.00)</t>
-        </is>
-      </c>
-      <c r="C30" s="43" t="n"/>
-      <c r="D30" s="43" t="n"/>
-    </row>
-    <row r="31" ht="28" customHeight="1" s="30">
-      <c r="A31" s="22" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Order Line 13  ·  Line Type N (non-stock, inventory interface = N)</t>
-        </is>
-      </c>
-      <c r="C31" s="42" t="n"/>
-      <c r="D31" s="42" t="n"/>
-    </row>
-    <row r="32" ht="16" customHeight="1" s="30">
-      <c r="A32" s="24" t="inlineStr">
-        <is>
-          <t>Branch</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>PLT2</t>
-        </is>
-      </c>
-      <c r="C32" s="43" t="n"/>
-      <c r="D32" s="43" t="n"/>
-    </row>
-    <row r="33" ht="16" customHeight="1" s="30">
-      <c r="A33" s="22" t="inlineStr">
-        <is>
-          <t>Document / GL Date</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Document DOC-00001 RI  ·  GL Date 2016-08-11</t>
-        </is>
-      </c>
-      <c r="C33" s="42" t="n"/>
-      <c r="D33" s="42" t="n"/>
-    </row>
-    <row r="34" ht="28" customHeight="1" s="30">
-      <c r="A34" s="26" t="inlineStr">
-        <is>
-          <t>Expected Account</t>
-        </is>
-      </c>
-      <c r="B34" s="20" t="inlineStr">
-        <is>
-          <t>Line type N should NEVER write a cardex and should NOT post to an inventory balance-sheet account</t>
-        </is>
-      </c>
-      <c r="C34" s="49" t="n"/>
-      <c r="D34" s="49" t="n"/>
-    </row>
-    <row r="35" ht="28" customHeight="1" s="30">
-      <c r="A35" s="26" t="inlineStr">
-        <is>
-          <t>Actual Account</t>
-        </is>
-      </c>
-      <c r="B35" s="20" t="inlineStr">
-        <is>
-          <t>GL credit landed in BU1.142000 — an inventory account per DMAAI 4152 model table for GL class BUYP</t>
-        </is>
-      </c>
-      <c r="C35" s="49" t="n"/>
-      <c r="D35" s="49" t="n"/>
-    </row>
-    <row r="36" ht="56" customHeight="1" s="30">
-      <c r="A36" s="28" t="inlineStr">
-        <is>
-          <t>Secondary Finding</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>Header Comp Line 4: doc = 0, GL date = 2000-01-01, comment = "sales ext cost error calc = 338.0000" — indicates an unprocessed or error line that never completed Sales Update</t>
-        </is>
-      </c>
-      <c r="C36" s="48" t="n"/>
-      <c r="D36" s="48" t="n"/>
-    </row>
-    <row r="37" ht="56" customHeight="1" s="30">
-      <c r="A37" s="22" t="inlineStr">
-        <is>
-          <t>DMAAI Gap</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>GL class FT60 has no entry in model table 4152 (Comment: "Missing model table entry"). Affects freight lines 8, 9, 10 which carry $0 cost — low priority but should be added for completeness.</t>
-        </is>
-      </c>
-      <c r="C37" s="42" t="n"/>
-      <c r="D37" s="42" t="n"/>
-    </row>
-    <row r="38" ht="16" customHeight="1" s="30">
-      <c r="A38" s="38" t="n"/>
-      <c r="B38" s="38" t="n"/>
-      <c r="C38" s="38" t="n"/>
-      <c r="D38" s="38" t="n"/>
-    </row>
-    <row r="39" ht="42" customHeight="1" s="30">
-      <c r="A39" s="52" t="inlineStr">
-        <is>
-          <t>5 · Evidence (Row References — Transaction Details Sheet)</t>
-        </is>
-      </c>
-      <c r="B39" s="53" t="n"/>
-      <c r="C39" s="53" t="n"/>
-      <c r="D39" s="53" t="n"/>
-    </row>
-    <row r="40" ht="28" customHeight="1" s="30">
-      <c r="A40" s="22" t="inlineStr">
-        <is>
-          <t>Doc Header (row 3)</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Period Apr 20 2026 · Doc DOC-00001 · DT RI · OrderNum ORD-00001 · OT SO · LedgerAmount $338</t>
-        </is>
-      </c>
-      <c r="C40" s="54" t="inlineStr">
-        <is>
-          <t>Orange highlight</t>
-        </is>
-      </c>
-      <c r="D40" s="42" t="n"/>
-    </row>
-    <row r="41" ht="42" customHeight="1" s="30">
-      <c r="A41" s="24" t="inlineStr">
-        <is>
-          <t>F0911 Inv entry (row 8)</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>Account BU1.142000 · Batch BATCH-00001 IB · Doc DOC-00001 RI · LedgerAmount ($338) · Comment: Non stock line in Inv acct</t>
-        </is>
-      </c>
-      <c r="C41" s="55" t="inlineStr">
-        <is>
-          <t>Orange highlight</t>
-        </is>
-      </c>
-      <c r="D41" s="43" t="n"/>
-    </row>
-    <row r="42" ht="16" customHeight="1" s="30">
-      <c r="A42" s="22" t="inlineStr">
-        <is>
-          <t>F0911 Tot (row 9)</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>GL Total ($338) — Inv Accounts Only</t>
-        </is>
-      </c>
-      <c r="C42" s="54" t="inlineStr">
-        <is>
-          <t>Orange highlight</t>
-        </is>
-      </c>
-      <c r="D42" s="42" t="n"/>
-    </row>
-    <row r="43" ht="16" customHeight="1" s="30">
-      <c r="A43" s="24" t="inlineStr">
-        <is>
-          <t>RR Summary (row 14)</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>CardexAmt $0 · LedgerAmt ($338) · Variance $338</t>
-        </is>
-      </c>
-      <c r="C43" s="55" t="inlineStr">
-        <is>
-          <t>Orange highlight</t>
-        </is>
-      </c>
-      <c r="D43" s="43" t="n"/>
-    </row>
-    <row r="44" ht="16" customHeight="1" s="30">
-      <c r="A44" s="22" t="inlineStr">
-        <is>
-          <t>RR Summary Tot (row 15)</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>RR Total: Cardex $0 · GL ($338) · Variance $338</t>
-        </is>
-      </c>
-      <c r="C44" s="54" t="inlineStr">
-        <is>
-          <t>Orange highlight</t>
-        </is>
-      </c>
-      <c r="D44" s="42" t="n"/>
-    </row>
-    <row r="45" ht="42" customHeight="1" s="30">
-      <c r="A45" s="26" t="inlineStr">
-        <is>
-          <t>Header Comp Line 13 (row 21)</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="inlineStr">
-        <is>
-          <t>Item ITEM-00004 · GL Class BUYP · Line Type N · Doc DOC-00001 RI · GL Date 2016-08-11 · Qty 1000 · UnitCost 0.338 · ExtAmt $338</t>
-        </is>
-      </c>
-      <c r="C45" s="56" t="inlineStr">
-        <is>
-          <t>RED — root cause</t>
-        </is>
-      </c>
-      <c r="D45" s="49" t="n"/>
-    </row>
-    <row r="46" ht="42" customHeight="1" s="30">
-      <c r="A46" s="26" t="inlineStr">
-        <is>
-          <t>Header Comp Line 4 (row 24)</t>
-        </is>
-      </c>
-      <c r="B46" s="20" t="inlineStr">
-        <is>
-          <t>Item ITEM-00004 · GL Class BUYP · Doc 0 · GL Date 2000-01-01 · comment: sales ext cost error calc = 338.0000</t>
-        </is>
-      </c>
-      <c r="C46" s="56" t="inlineStr">
-        <is>
-          <t>RED — secondary</t>
-        </is>
-      </c>
-      <c r="D46" s="49" t="n"/>
-    </row>
-    <row r="47" ht="28" customHeight="1" s="30">
-      <c r="A47" s="24" t="inlineStr">
-        <is>
-          <t>DMAAI row 35</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t>GL Class FT60 · 4152 Inv Model · Comment: Missing model table entry</t>
-        </is>
-      </c>
-      <c r="C47" s="55" t="inlineStr">
-        <is>
-          <t>No highlight (informational)</t>
-        </is>
-      </c>
-      <c r="D47" s="43" t="n"/>
-    </row>
-    <row r="48" ht="16" customHeight="1" s="30">
-      <c r="A48" s="38" t="n"/>
-      <c r="B48" s="38" t="n"/>
-      <c r="C48" s="38" t="n"/>
-      <c r="D48" s="38" t="n"/>
-    </row>
-    <row r="49" ht="16" customHeight="1" s="30">
-      <c r="A49" s="52" t="inlineStr">
-        <is>
-          <t>6 · Recommended Actions</t>
-        </is>
-      </c>
-      <c r="B49" s="53" t="n"/>
-      <c r="C49" s="53" t="n"/>
-      <c r="D49" s="53" t="n"/>
-    </row>
-    <row r="50" ht="70" customHeight="1" s="30">
-      <c r="A50" s="28" t="inlineStr">
-        <is>
-          <t>1 · Assess Materiality</t>
-        </is>
-      </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>At $338.00 and approximately 10 years old (August 2016), evaluate against your materiality threshold before posting a correcting entry. If below threshold, consider suspending in RapidReconciler with a documented note.</t>
-        </is>
-      </c>
-      <c r="C50" s="48" t="n"/>
-      <c r="D50" s="48" t="n"/>
-    </row>
-    <row r="51" ht="98" customHeight="1" s="30">
-      <c r="A51" s="28" t="inlineStr">
-        <is>
-          <t>2 · Journal Entry (if required)</t>
-        </is>
-      </c>
-      <c r="B51" s="17" t="inlineStr">
-        <is>
-          <t>Debit: BU2.501010 (COGS — AAI 4220 for GL class BUYP)  $338.00
-Credit: BU1.142000 (Inventory account — AAI 4152/4240 for GL class BUYP)  $338.00
-Description: Reclassify non-stock line (ITEM-00004, SO ORD-00001 line 13) from inventory to expense — correcting IB batch BATCH-00001.</t>
-        </is>
-      </c>
-      <c r="C51" s="48" t="n"/>
-      <c r="D51" s="48" t="n"/>
-    </row>
-    <row r="52" ht="84" customHeight="1" s="30">
-      <c r="A52" s="22" t="inlineStr">
-        <is>
-          <t>3 · Investigate Batch BATCH-00001 IB</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>A non-stock line (line type N) should never post to an inventory balance-sheet account. Identify who created IB batch BATCH-00001 and why it was coded to account BU1.142000 instead of the COGS/expense account. Determine if other lines in this batch have the same coding error.</t>
-        </is>
-      </c>
-      <c r="C52" s="42" t="n"/>
-      <c r="D52" s="42" t="n"/>
-    </row>
-    <row r="53" ht="84" customHeight="1" s="30">
-      <c r="A53" s="24" t="inlineStr">
-        <is>
-          <t>4 · Investigate Header Comp Line 4</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>Line 4 shows doc = 0 and GL date = 2000-01-01 with comment "sales ext cost error calc = 338.0000." This indicates the line was never processed through Sales Update. Confirm in JD Edwards whether this line requires processing or whether the order can be closed.</t>
-        </is>
-      </c>
-      <c r="C53" s="43" t="n"/>
-      <c r="D53" s="43" t="n"/>
-    </row>
-    <row r="54" ht="56" customHeight="1" s="30">
-      <c r="A54" s="22" t="inlineStr">
-        <is>
-          <t>5 · Add FT60 to Model Table 4152</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>GL class FT60 is missing from DMAAI model table 4152. Add it to ensure complete reconciliation coverage. Low priority as all FT60 freight lines on this order carry zero cost.</t>
-        </is>
-      </c>
-      <c r="C54" s="42" t="n"/>
-      <c r="D54" s="42" t="n"/>
-    </row>
-    <row r="55" ht="70" customHeight="1" s="30">
-      <c r="A55" s="24" t="inlineStr">
-        <is>
-          <t>6 · Document in RapidReconciler</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>Add a note to document DOC-00001 RI in RapidReconciler recording the root cause (non-stock line type N incorrectly posted to inventory via IB batch), the corrective action taken, and date completed. Mark as Worked once resolved.</t>
-        </is>
-      </c>
-      <c r="C55" s="43" t="n"/>
-      <c r="D55" s="43" t="n"/>
-    </row>
-    <row r="56" ht="16" customHeight="1" s="30">
-      <c r="A56" s="38" t="n"/>
-      <c r="B56" s="38" t="n"/>
-      <c r="C56" s="38" t="n"/>
-      <c r="D56" s="38" t="n"/>
-    </row>
-    <row r="57" ht="56" customHeight="1" s="30">
-      <c r="A57" s="57" t="inlineStr">
-        <is>
-          <t>Analysis produced using Transaction Detail Analysis Guide · RapidReconciler Inventory · April 21, 2026</t>
+      <c r="B7" s="68" t="n"/>
+      <c r="C7" s="69" t="inlineStr">
+        <is>
+          <t>Pattern:  GL-Only Entry — Non-stock line posted to inventory account
+$338.00 variance vs $338.00 document amount = 100%  →  Priority 1</t>
+        </is>
+      </c>
+      <c r="D7" s="68" t="n"/>
+      <c r="E7" s="68" t="n"/>
+    </row>
+    <row r="8" ht="14" customHeight="1" s="30"/>
+    <row r="9" ht="28" customHeight="1" s="30">
+      <c r="A9" s="70" t="inlineStr">
+        <is>
+          <t>1.  WHAT happened</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="130" customHeight="1" s="30">
+      <c r="A10" s="71" t="inlineStr">
+        <is>
+          <t>An IB-batch journal entry posted a $338.00 credit to inventory account BU1.142000 — but no cardex (F4111) row exists for this document.
+RapidReconciler flagged the entry with the comment “Non stock line in Inv acct,” confirming the GL side is real and the cardex side is empty.  The entire $338 GL entry is the variance.</t>
+        </is>
+      </c>
+      <c r="B10" s="72" t="n"/>
+      <c r="C10" s="72" t="n"/>
+      <c r="D10" s="72" t="n"/>
+      <c r="E10" s="72" t="n"/>
+    </row>
+    <row r="11" ht="28" customHeight="1" s="30">
+      <c r="A11" s="73" t="inlineStr">
+        <is>
+          <t>2.  WHY it happened</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="160" customHeight="1" s="30">
+      <c r="A12" s="74" t="inlineStr">
+        <is>
+          <t>Order line 13 is line type N (non-stock), item ITEM-00004, GL class BUYP, 1,000 EA × $0.338.  Non-stock lines should never write a cardex record and should never post to a balance-sheet inventory account.
+Someone created IB batch BATCH-00001 that booked the value to BU1.142000 instead of the correct COGS or expense account.  A secondary indicator on Header Comp line 4 (doc 0, GL date 2000-01-01, comment “sales ext cost error calc = 338.0000”) suggests an unprocessed line that never completed Sales Update — this is likely the same value that was later booked manually via the IB batch.</t>
+        </is>
+      </c>
+      <c r="B12" s="75" t="n"/>
+      <c r="C12" s="75" t="n"/>
+      <c r="D12" s="75" t="n"/>
+      <c r="E12" s="75" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1" s="30">
+      <c r="A13" s="70" t="inlineStr">
+        <is>
+          <t>3.  HOW to fix it</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="290" customHeight="1" s="30">
+      <c r="A14" s="71" t="inlineStr">
+        <is>
+          <t>Step 1.  Reclassify the $338.00 from inventory to COGS by posting this journal entry:
+    DR  BU2.501010  COGS (AAI 4220, GL class BUYP)  $338.00
+    CR  BU1.142000  Inventory (AAI 4152, GL class BUYP)  $338.00
+Step 2.  Investigate IB batch BATCH-00001 — identify who created it and why it was coded to the inventory account.  A non-stock line should never reach a balance-sheet inventory account, so an IB batch posting one is a control gap that should be closed.
+Step 3.  Investigate Header Comp line 4 (doc 0, GL date 2000-01-01).  Confirm in JD Edwards whether this line was meant to be processed through Sales Update.  If yes, the IB-batch correction has already fixed the GL impact and no further action is needed; if no, work with the order desk to close the line cleanly.
+Step 4.  Add GL class FT60 to DMAAI model table 4152.  Low priority — all FT60 freight lines on this order carry zero cost — but worth doing for completeness so future freight transactions reconcile cleanly.
+Step 5.  At $338 and approximately 10 years old (August 2016), evaluate the materiality of this entry against your threshold before posting the correction.  If below threshold, consider suspending in RapidReconciler instead of posting a correcting entry.</t>
+        </is>
+      </c>
+      <c r="B14" s="72" t="n"/>
+      <c r="C14" s="72" t="n"/>
+      <c r="D14" s="72" t="n"/>
+      <c r="E14" s="72" t="n"/>
+    </row>
+    <row r="15" ht="14" customHeight="1" s="30"/>
+    <row r="16" ht="40" customHeight="1" s="30">
+      <c r="A16" s="76" t="inlineStr">
+        <is>
+          <t>Evidence  (click to jump to the row on the Transaction Details sheet)</t>
+        </is>
+      </c>
+      <c r="C16" s="77" t="n"/>
+      <c r="E16" s="78" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1" s="30">
+      <c r="A17" s="79" t="inlineStr">
+        <is>
+          <t>GL credit  →  Row 8</t>
+        </is>
+      </c>
+      <c r="C17" s="80" t="inlineStr">
+        <is>
+          <t>Inv account BU1.142000 · Batch BATCH-00001 IB · ($338.00)
+Comment: Non stock line in Inv acct</t>
+        </is>
+      </c>
+      <c r="E17" s="81" t="inlineStr">
+        <is>
+          <t>Root cause</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1" s="30">
+      <c r="A18" s="79" t="inlineStr">
+        <is>
+          <t>Order line 13  →  Row 21</t>
+        </is>
+      </c>
+      <c r="C18" s="80" t="inlineStr">
+        <is>
+          <t>Item ITEM-00004 · Line type N · Qty 1,000 × $0.338
+GL class BUYP · GL date 2016-08-11</t>
+        </is>
+      </c>
+      <c r="E18" s="81" t="inlineStr">
+        <is>
+          <t>Root cause</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="1" s="30">
+      <c r="A19" s="79" t="inlineStr">
+        <is>
+          <t>Order line 4  →  Row 24</t>
+        </is>
+      </c>
+      <c r="C19" s="80" t="inlineStr">
+        <is>
+          <t>Doc 0 · GL date 2000-01-01
+Comment: sales ext cost error calc = 338.0000</t>
+        </is>
+      </c>
+      <c r="E19" s="82" t="inlineStr">
+        <is>
+          <t>Related</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1" s="30">
+      <c r="A20" s="79" t="inlineStr">
+        <is>
+          <t>RR Summary  →  Row 14</t>
+        </is>
+      </c>
+      <c r="C20" s="80" t="inlineStr">
+        <is>
+          <t>CardexAmt $0.00 · LedgerAmt ($338.00) · Variance $338.00
+Where the variance shows</t>
+        </is>
+      </c>
+      <c r="E20" s="82" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1" s="30">
+      <c r="A21" s="79" t="inlineStr">
+        <is>
+          <t>DMAAI gap  →  Row 35</t>
+        </is>
+      </c>
+      <c r="C21" s="80" t="inlineStr">
+        <is>
+          <t>GL class FT60 missing from model table 4152
+Affects $0 freight lines — low priority</t>
+        </is>
+      </c>
+      <c r="E21" s="83" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="12" customHeight="1" s="30"/>
+    <row r="23" ht="70" customHeight="1" s="30">
+      <c r="A23" s="84" t="inlineStr">
+        <is>
+          <t>⚠  Before making any changes in JD Edwards:  test all configuration changes in a non-production environment first. For any GL journal entry, review the Transactions page in RapidReconciler for the affected items to confirm exact amounts and accounts before posting.</t>
+        </is>
+      </c>
+      <c r="B23" s="85" t="n"/>
+      <c r="C23" s="85" t="n"/>
+      <c r="D23" s="85" t="n"/>
+      <c r="E23" s="85" t="n"/>
+    </row>
+    <row r="24" ht="8" customHeight="1" s="30"/>
+    <row r="25" ht="18" customHeight="1" s="30">
+      <c r="A25" s="86" t="inlineStr">
+        <is>
+          <t>Analysis produced using the Transaction Detail Analysis Guide  ·  RapidReconciler  ·  April 25 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A2:D2"/>
+  <mergeCells count="26">
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId100"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId5"/>
+  </hyperlinks>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="3" fitToHeight="1" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
 </worksheet>
 </file>
 
@@ -2002,2544 +1707,3449 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="58" t="n"/>
-      <c r="B3" s="58" t="inlineStr">
+      <c r="A3" s="87" t="n"/>
+      <c r="B3" s="87" t="inlineStr">
         <is>
           <t xml:space="preserve">Apr 20 2026                             </t>
         </is>
       </c>
-      <c r="C3" s="58" t="inlineStr">
+      <c r="C3" s="87" t="inlineStr">
         <is>
           <t>Doc Header</t>
         </is>
       </c>
-      <c r="D3" s="58" t="inlineStr">
+      <c r="D3" s="87" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="E3" s="58" t="n"/>
-      <c r="F3" s="58" t="n"/>
-      <c r="G3" s="58" t="n"/>
-      <c r="H3" s="58" t="n"/>
-      <c r="I3" s="58" t="n"/>
-      <c r="J3" s="58" t="inlineStr">
+      <c r="E3" s="87" t="n"/>
+      <c r="F3" s="87" t="n"/>
+      <c r="G3" s="87" t="n"/>
+      <c r="H3" s="87" t="n"/>
+      <c r="I3" s="87" t="n"/>
+      <c r="J3" s="87" t="inlineStr">
         <is>
           <t xml:space="preserve">DOC-00001 </t>
         </is>
       </c>
-      <c r="K3" s="58" t="inlineStr">
+      <c r="K3" s="87" t="inlineStr">
         <is>
           <t xml:space="preserve">RI     </t>
         </is>
       </c>
-      <c r="L3" s="58" t="inlineStr">
+      <c r="L3" s="87" t="inlineStr">
         <is>
           <t xml:space="preserve">ORD-00001 </t>
         </is>
       </c>
-      <c r="M3" s="58" t="inlineStr">
+      <c r="M3" s="87" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="N3" s="58" t="n"/>
-      <c r="O3" s="58" t="n"/>
-      <c r="P3" s="58" t="n"/>
-      <c r="Q3" s="58" t="n"/>
-      <c r="R3" s="58" t="n"/>
-      <c r="S3" s="58" t="n"/>
-      <c r="T3" s="58" t="n"/>
-      <c r="U3" s="58" t="n"/>
-      <c r="V3" s="58" t="n"/>
-      <c r="W3" s="58" t="n"/>
-      <c r="X3" s="58" t="n"/>
-      <c r="Y3" s="58" t="n"/>
-      <c r="Z3" s="58" t="n">
+      <c r="N3" s="87" t="n"/>
+      <c r="O3" s="87" t="n"/>
+      <c r="P3" s="87" t="n"/>
+      <c r="Q3" s="87" t="n"/>
+      <c r="R3" s="87" t="n"/>
+      <c r="S3" s="87" t="n"/>
+      <c r="T3" s="87" t="n"/>
+      <c r="U3" s="87" t="n"/>
+      <c r="V3" s="87" t="n"/>
+      <c r="W3" s="87" t="n"/>
+      <c r="X3" s="87" t="n"/>
+      <c r="Y3" s="87" t="n"/>
+      <c r="Z3" s="87" t="n">
         <v>338</v>
       </c>
-      <c r="AA3" s="58" t="n"/>
-      <c r="AB3" s="58" t="n"/>
-      <c r="AC3" s="58" t="n"/>
+      <c r="AA3" s="87" t="n"/>
+      <c r="AB3" s="87" t="n"/>
+      <c r="AC3" s="87" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="88" t="n"/>
+      <c r="B4" s="88" t="n"/>
+      <c r="C4" s="88" t="n"/>
+      <c r="D4" s="88" t="n"/>
+      <c r="E4" s="88" t="n"/>
+      <c r="F4" s="88" t="n"/>
+      <c r="G4" s="88" t="n"/>
+      <c r="H4" s="88" t="n"/>
+      <c r="I4" s="88" t="n"/>
+      <c r="J4" s="88" t="n"/>
+      <c r="K4" s="88" t="n"/>
+      <c r="L4" s="88" t="n"/>
+      <c r="M4" s="88" t="n"/>
+      <c r="N4" s="88" t="n"/>
+      <c r="O4" s="88" t="n"/>
+      <c r="P4" s="88" t="n"/>
+      <c r="Q4" s="88" t="n"/>
+      <c r="R4" s="88" t="n"/>
+      <c r="S4" s="88" t="n"/>
+      <c r="T4" s="88" t="n"/>
+      <c r="U4" s="88" t="n"/>
+      <c r="V4" s="88" t="n"/>
+      <c r="W4" s="88" t="n"/>
+      <c r="X4" s="88" t="n"/>
+      <c r="Y4" s="88" t="n"/>
+      <c r="Z4" s="88" t="n"/>
+      <c r="AA4" s="88" t="n"/>
+      <c r="AB4" s="88" t="n"/>
+      <c r="AC4" s="88" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="88" t="n"/>
+      <c r="B5" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">F4111 Data                              </t>
         </is>
       </c>
+      <c r="C5" s="88" t="n"/>
+      <c r="D5" s="88" t="n"/>
+      <c r="E5" s="88" t="n"/>
+      <c r="F5" s="88" t="n"/>
+      <c r="G5" s="88" t="n"/>
+      <c r="H5" s="88" t="n"/>
+      <c r="I5" s="88" t="n"/>
+      <c r="J5" s="88" t="n"/>
+      <c r="K5" s="88" t="n"/>
+      <c r="L5" s="88" t="n"/>
+      <c r="M5" s="88" t="n"/>
+      <c r="N5" s="88" t="n"/>
+      <c r="O5" s="88" t="n"/>
+      <c r="P5" s="88" t="n"/>
+      <c r="Q5" s="88" t="n"/>
+      <c r="R5" s="88" t="n"/>
+      <c r="S5" s="88" t="n"/>
+      <c r="T5" s="88" t="n"/>
+      <c r="U5" s="88" t="n"/>
+      <c r="V5" s="88" t="n"/>
+      <c r="W5" s="88" t="n"/>
+      <c r="X5" s="88" t="n"/>
+      <c r="Y5" s="88" t="n"/>
+      <c r="Z5" s="88" t="n"/>
+      <c r="AA5" s="88" t="n"/>
+      <c r="AB5" s="88" t="n"/>
+      <c r="AC5" s="88" t="n"/>
     </row>
     <row r="6">
-      <c r="C6" t="inlineStr">
+      <c r="A6" s="88" t="n"/>
+      <c r="B6" s="88" t="n"/>
+      <c r="C6" s="88" t="inlineStr">
         <is>
           <t>F4111 Tot</t>
         </is>
       </c>
-      <c r="X6" t="n">
+      <c r="D6" s="88" t="n"/>
+      <c r="E6" s="88" t="n"/>
+      <c r="F6" s="88" t="n"/>
+      <c r="G6" s="88" t="n"/>
+      <c r="H6" s="88" t="n"/>
+      <c r="I6" s="88" t="n"/>
+      <c r="J6" s="88" t="n"/>
+      <c r="K6" s="88" t="n"/>
+      <c r="L6" s="88" t="n"/>
+      <c r="M6" s="88" t="n"/>
+      <c r="N6" s="88" t="n"/>
+      <c r="O6" s="88" t="n"/>
+      <c r="P6" s="88" t="n"/>
+      <c r="Q6" s="88" t="n"/>
+      <c r="R6" s="88" t="n"/>
+      <c r="S6" s="88" t="n"/>
+      <c r="T6" s="88" t="n"/>
+      <c r="U6" s="88" t="n"/>
+      <c r="V6" s="88" t="n"/>
+      <c r="W6" s="88" t="n"/>
+      <c r="X6" s="88" t="n">
         <v>0</v>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="Y6" s="88" t="n"/>
+      <c r="Z6" s="88" t="n"/>
+      <c r="AA6" s="88" t="inlineStr">
         <is>
           <t>Cardex Total</t>
         </is>
       </c>
+      <c r="AB6" s="88" t="n"/>
+      <c r="AC6" s="88" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
+      <c r="A7" s="88" t="n"/>
+      <c r="B7" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">F0911 Inv Acct                          </t>
         </is>
       </c>
+      <c r="C7" s="88" t="n"/>
+      <c r="D7" s="88" t="n"/>
+      <c r="E7" s="88" t="n"/>
+      <c r="F7" s="88" t="n"/>
+      <c r="G7" s="88" t="n"/>
+      <c r="H7" s="88" t="n"/>
+      <c r="I7" s="88" t="n"/>
+      <c r="J7" s="88" t="n"/>
+      <c r="K7" s="88" t="n"/>
+      <c r="L7" s="88" t="n"/>
+      <c r="M7" s="88" t="n"/>
+      <c r="N7" s="88" t="n"/>
+      <c r="O7" s="88" t="n"/>
+      <c r="P7" s="88" t="n"/>
+      <c r="Q7" s="88" t="n"/>
+      <c r="R7" s="88" t="n"/>
+      <c r="S7" s="88" t="n"/>
+      <c r="T7" s="88" t="n"/>
+      <c r="U7" s="88" t="n"/>
+      <c r="V7" s="88" t="n"/>
+      <c r="W7" s="88" t="n"/>
+      <c r="X7" s="88" t="n"/>
+      <c r="Y7" s="88" t="n"/>
+      <c r="Z7" s="88" t="n"/>
+      <c r="AA7" s="88" t="n"/>
+      <c r="AB7" s="88" t="n"/>
+      <c r="AC7" s="88" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="58" t="inlineStr">
+      <c r="A8" s="89" t="inlineStr">
         <is>
           <t>2016-08-27</t>
         </is>
       </c>
-      <c r="B8" s="58" t="inlineStr">
+      <c r="B8" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">BU1.142000                          </t>
         </is>
       </c>
-      <c r="C8" s="58" t="inlineStr">
+      <c r="C8" s="89" t="inlineStr">
         <is>
           <t>F0911 Inv</t>
         </is>
       </c>
-      <c r="D8" s="58" t="inlineStr">
+      <c r="D8" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="E8" s="58" t="inlineStr">
+      <c r="E8" s="89" t="inlineStr">
         <is>
           <t>2016-08-12</t>
         </is>
       </c>
-      <c r="F8" s="58" t="inlineStr">
+      <c r="F8" s="89" t="inlineStr">
         <is>
           <t>2016-08-11</t>
         </is>
       </c>
-      <c r="G8" s="58" t="n"/>
-      <c r="H8" s="58" t="inlineStr">
+      <c r="G8" s="89" t="n"/>
+      <c r="H8" s="89" t="inlineStr">
         <is>
           <t>BATCH-00001</t>
         </is>
       </c>
-      <c r="I8" s="58" t="inlineStr">
+      <c r="I8" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">IB    </t>
         </is>
       </c>
-      <c r="J8" s="58" t="inlineStr">
+      <c r="J8" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">DOC-00001 </t>
         </is>
       </c>
-      <c r="K8" s="58" t="inlineStr">
+      <c r="K8" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">RI     </t>
         </is>
       </c>
-      <c r="L8" s="58" t="inlineStr">
+      <c r="L8" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">ORD-00001 </t>
         </is>
       </c>
-      <c r="M8" s="58" t="inlineStr">
+      <c r="M8" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="N8" s="58" t="inlineStr">
+      <c r="N8" s="89" t="inlineStr">
         <is>
           <t>13.000</t>
         </is>
       </c>
-      <c r="O8" s="58" t="inlineStr">
+      <c r="O8" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">      </t>
         </is>
       </c>
-      <c r="P8" s="58" t="inlineStr">
+      <c r="P8" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">P     </t>
         </is>
       </c>
-      <c r="Q8" s="58" t="n"/>
-      <c r="R8" s="58" t="inlineStr">
+      <c r="Q8" s="89" t="n"/>
+      <c r="R8" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">ITEM-00004               </t>
         </is>
       </c>
-      <c r="S8" s="58" t="n"/>
-      <c r="T8" s="58" t="n"/>
-      <c r="U8" s="58" t="n"/>
-      <c r="V8" s="58" t="n"/>
-      <c r="W8" s="58" t="n"/>
-      <c r="X8" s="58" t="n"/>
-      <c r="Y8" s="58" t="n">
+      <c r="S8" s="89" t="n"/>
+      <c r="T8" s="89" t="n"/>
+      <c r="U8" s="89" t="n"/>
+      <c r="V8" s="89" t="n"/>
+      <c r="W8" s="89" t="n"/>
+      <c r="X8" s="89" t="n"/>
+      <c r="Y8" s="89" t="n">
         <v>-338</v>
       </c>
-      <c r="Z8" s="58" t="n"/>
-      <c r="AA8" s="58" t="n"/>
-      <c r="AB8" s="58" t="inlineStr">
+      <c r="Z8" s="89" t="n"/>
+      <c r="AA8" s="89" t="n"/>
+      <c r="AB8" s="89" t="inlineStr">
         <is>
           <t>Non stock line in Inv acct</t>
         </is>
       </c>
-      <c r="AC8" s="58" t="n"/>
+      <c r="AC8" s="89" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="58" t="n"/>
-      <c r="B9" s="58" t="n"/>
-      <c r="C9" s="58" t="inlineStr">
+      <c r="A9" s="88" t="n"/>
+      <c r="B9" s="88" t="n"/>
+      <c r="C9" s="88" t="inlineStr">
         <is>
           <t>F0911 Tot</t>
         </is>
       </c>
-      <c r="D9" s="58" t="n"/>
-      <c r="E9" s="58" t="n"/>
-      <c r="F9" s="58" t="n"/>
-      <c r="G9" s="58" t="n"/>
-      <c r="H9" s="58" t="n"/>
-      <c r="I9" s="58" t="n"/>
-      <c r="J9" s="58" t="n"/>
-      <c r="K9" s="58" t="n"/>
-      <c r="L9" s="58" t="n"/>
-      <c r="M9" s="58" t="n"/>
-      <c r="N9" s="58" t="n"/>
-      <c r="O9" s="58" t="n"/>
-      <c r="P9" s="58" t="n"/>
-      <c r="Q9" s="58" t="n"/>
-      <c r="R9" s="58" t="n"/>
-      <c r="S9" s="58" t="n"/>
-      <c r="T9" s="58" t="n"/>
-      <c r="U9" s="58" t="n"/>
-      <c r="V9" s="58" t="n"/>
-      <c r="W9" s="58" t="n"/>
-      <c r="X9" s="58" t="n"/>
-      <c r="Y9" s="58" t="n">
+      <c r="D9" s="88" t="n"/>
+      <c r="E9" s="88" t="n"/>
+      <c r="F9" s="88" t="n"/>
+      <c r="G9" s="88" t="n"/>
+      <c r="H9" s="88" t="n"/>
+      <c r="I9" s="88" t="n"/>
+      <c r="J9" s="88" t="n"/>
+      <c r="K9" s="88" t="n"/>
+      <c r="L9" s="88" t="n"/>
+      <c r="M9" s="88" t="n"/>
+      <c r="N9" s="88" t="n"/>
+      <c r="O9" s="88" t="n"/>
+      <c r="P9" s="88" t="n"/>
+      <c r="Q9" s="88" t="n"/>
+      <c r="R9" s="88" t="n"/>
+      <c r="S9" s="88" t="n"/>
+      <c r="T9" s="88" t="n"/>
+      <c r="U9" s="88" t="n"/>
+      <c r="V9" s="88" t="n"/>
+      <c r="W9" s="88" t="n"/>
+      <c r="X9" s="88" t="n"/>
+      <c r="Y9" s="88" t="n">
         <v>-338</v>
       </c>
-      <c r="Z9" s="58" t="n"/>
-      <c r="AA9" s="58" t="inlineStr">
+      <c r="Z9" s="88" t="n"/>
+      <c r="AA9" s="88" t="inlineStr">
         <is>
           <t>GL Total</t>
         </is>
       </c>
-      <c r="AB9" s="58" t="inlineStr">
+      <c r="AB9" s="88" t="inlineStr">
         <is>
           <t>Inv Accounts Only</t>
         </is>
       </c>
-      <c r="AC9" s="58" t="n"/>
+      <c r="AC9" s="88" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="88" t="n"/>
+      <c r="B10" s="88" t="n"/>
+      <c r="C10" s="88" t="n"/>
+      <c r="D10" s="88" t="n"/>
+      <c r="E10" s="88" t="n"/>
+      <c r="F10" s="88" t="n"/>
+      <c r="G10" s="88" t="n"/>
+      <c r="H10" s="88" t="n"/>
+      <c r="I10" s="88" t="n"/>
+      <c r="J10" s="88" t="n"/>
+      <c r="K10" s="88" t="n"/>
+      <c r="L10" s="88" t="n"/>
+      <c r="M10" s="88" t="n"/>
+      <c r="N10" s="88" t="n"/>
+      <c r="O10" s="88" t="n"/>
+      <c r="P10" s="88" t="n"/>
+      <c r="Q10" s="88" t="n"/>
+      <c r="R10" s="88" t="n"/>
+      <c r="S10" s="88" t="n"/>
+      <c r="T10" s="88" t="n"/>
+      <c r="U10" s="88" t="n"/>
+      <c r="V10" s="88" t="n"/>
+      <c r="W10" s="88" t="n"/>
+      <c r="X10" s="88" t="n"/>
+      <c r="Y10" s="88" t="n"/>
+      <c r="Z10" s="88" t="n"/>
+      <c r="AA10" s="88" t="n"/>
+      <c r="AB10" s="88" t="n"/>
+      <c r="AC10" s="88" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="88" t="n"/>
+      <c r="B11" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">F0911 Exp Acct                          </t>
         </is>
       </c>
+      <c r="C11" s="88" t="n"/>
+      <c r="D11" s="88" t="n"/>
+      <c r="E11" s="88" t="n"/>
+      <c r="F11" s="88" t="n"/>
+      <c r="G11" s="88" t="n"/>
+      <c r="H11" s="88" t="n"/>
+      <c r="I11" s="88" t="n"/>
+      <c r="J11" s="88" t="n"/>
+      <c r="K11" s="88" t="n"/>
+      <c r="L11" s="88" t="n"/>
+      <c r="M11" s="88" t="n"/>
+      <c r="N11" s="88" t="n"/>
+      <c r="O11" s="88" t="n"/>
+      <c r="P11" s="88" t="n"/>
+      <c r="Q11" s="88" t="n"/>
+      <c r="R11" s="88" t="n"/>
+      <c r="S11" s="88" t="n"/>
+      <c r="T11" s="88" t="n"/>
+      <c r="U11" s="88" t="n"/>
+      <c r="V11" s="88" t="n"/>
+      <c r="W11" s="88" t="n"/>
+      <c r="X11" s="88" t="n"/>
+      <c r="Y11" s="88" t="n"/>
+      <c r="Z11" s="88" t="n"/>
+      <c r="AA11" s="88" t="n"/>
+      <c r="AB11" s="88" t="n"/>
+      <c r="AC11" s="88" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="88" t="n"/>
+      <c r="B12" s="88" t="n"/>
+      <c r="C12" s="88" t="n"/>
+      <c r="D12" s="88" t="n"/>
+      <c r="E12" s="88" t="n"/>
+      <c r="F12" s="88" t="n"/>
+      <c r="G12" s="88" t="n"/>
+      <c r="H12" s="88" t="n"/>
+      <c r="I12" s="88" t="n"/>
+      <c r="J12" s="88" t="n"/>
+      <c r="K12" s="88" t="n"/>
+      <c r="L12" s="88" t="n"/>
+      <c r="M12" s="88" t="n"/>
+      <c r="N12" s="88" t="n"/>
+      <c r="O12" s="88" t="n"/>
+      <c r="P12" s="88" t="n"/>
+      <c r="Q12" s="88" t="n"/>
+      <c r="R12" s="88" t="n"/>
+      <c r="S12" s="88" t="n"/>
+      <c r="T12" s="88" t="n"/>
+      <c r="U12" s="88" t="n"/>
+      <c r="V12" s="88" t="n"/>
+      <c r="W12" s="88" t="n"/>
+      <c r="X12" s="88" t="n"/>
+      <c r="Y12" s="88" t="n"/>
+      <c r="Z12" s="88" t="n"/>
+      <c r="AA12" s="88" t="n"/>
+      <c r="AB12" s="88" t="n"/>
+      <c r="AC12" s="88" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="88" t="n"/>
+      <c r="B13" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">RR Summary                              </t>
         </is>
       </c>
+      <c r="C13" s="88" t="n"/>
+      <c r="D13" s="88" t="n"/>
+      <c r="E13" s="88" t="n"/>
+      <c r="F13" s="88" t="n"/>
+      <c r="G13" s="88" t="n"/>
+      <c r="H13" s="88" t="n"/>
+      <c r="I13" s="88" t="n"/>
+      <c r="J13" s="88" t="n"/>
+      <c r="K13" s="88" t="n"/>
+      <c r="L13" s="88" t="n"/>
+      <c r="M13" s="88" t="n"/>
+      <c r="N13" s="88" t="n"/>
+      <c r="O13" s="88" t="n"/>
+      <c r="P13" s="88" t="n"/>
+      <c r="Q13" s="88" t="n"/>
+      <c r="R13" s="88" t="n"/>
+      <c r="S13" s="88" t="n"/>
+      <c r="T13" s="88" t="n"/>
+      <c r="U13" s="88" t="n"/>
+      <c r="V13" s="88" t="n"/>
+      <c r="W13" s="88" t="n"/>
+      <c r="X13" s="88" t="n"/>
+      <c r="Y13" s="88" t="n"/>
+      <c r="Z13" s="88" t="n"/>
+      <c r="AA13" s="88" t="n"/>
+      <c r="AB13" s="88" t="n"/>
+      <c r="AC13" s="88" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="58" t="inlineStr">
+      <c r="A14" s="90" t="inlineStr">
         <is>
           <t>2016-08-27</t>
         </is>
       </c>
-      <c r="B14" s="58" t="inlineStr">
+      <c r="B14" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">BU1.142000                          </t>
         </is>
       </c>
-      <c r="C14" s="58" t="inlineStr">
+      <c r="C14" s="90" t="inlineStr">
         <is>
           <t>RapidRec</t>
         </is>
       </c>
-      <c r="D14" s="58" t="inlineStr">
+      <c r="D14" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="E14" s="58" t="n"/>
-      <c r="F14" s="58" t="n"/>
-      <c r="G14" s="58" t="n"/>
-      <c r="H14" s="58" t="inlineStr">
+      <c r="E14" s="90" t="n"/>
+      <c r="F14" s="90" t="n"/>
+      <c r="G14" s="90" t="n"/>
+      <c r="H14" s="90" t="inlineStr">
         <is>
           <t>BATCH-00001</t>
         </is>
       </c>
-      <c r="I14" s="58" t="inlineStr">
+      <c r="I14" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">IB    </t>
         </is>
       </c>
-      <c r="J14" s="58" t="inlineStr">
+      <c r="J14" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">DOC-00001 </t>
         </is>
       </c>
-      <c r="K14" s="58" t="inlineStr">
+      <c r="K14" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">RI     </t>
         </is>
       </c>
-      <c r="L14" s="58" t="inlineStr">
+      <c r="L14" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">ORD-00001 </t>
         </is>
       </c>
-      <c r="M14" s="58" t="inlineStr">
+      <c r="M14" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="N14" s="58" t="n"/>
-      <c r="O14" s="58" t="n"/>
-      <c r="P14" s="58" t="n"/>
-      <c r="Q14" s="58" t="n"/>
-      <c r="R14" s="58" t="n"/>
-      <c r="S14" s="58" t="n"/>
-      <c r="T14" s="58" t="n"/>
-      <c r="U14" s="58" t="n"/>
-      <c r="V14" s="58" t="n"/>
-      <c r="W14" s="58" t="n"/>
-      <c r="X14" s="58" t="n">
+      <c r="N14" s="90" t="n"/>
+      <c r="O14" s="90" t="n"/>
+      <c r="P14" s="90" t="n"/>
+      <c r="Q14" s="90" t="n"/>
+      <c r="R14" s="90" t="n"/>
+      <c r="S14" s="90" t="n"/>
+      <c r="T14" s="90" t="n"/>
+      <c r="U14" s="90" t="n"/>
+      <c r="V14" s="90" t="n"/>
+      <c r="W14" s="90" t="n"/>
+      <c r="X14" s="90" t="n">
         <v>0</v>
       </c>
-      <c r="Y14" s="58" t="n">
+      <c r="Y14" s="90" t="n">
         <v>-338</v>
       </c>
-      <c r="Z14" s="58" t="n">
+      <c r="Z14" s="90" t="n">
         <v>-338</v>
       </c>
-      <c r="AA14" s="58" t="n"/>
-      <c r="AB14" s="58" t="n"/>
-      <c r="AC14" s="58" t="n"/>
+      <c r="AA14" s="90" t="n"/>
+      <c r="AB14" s="90" t="n"/>
+      <c r="AC14" s="90" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="58" t="n"/>
-      <c r="B15" s="58" t="n"/>
-      <c r="C15" s="58" t="inlineStr">
+      <c r="A15" s="88" t="n"/>
+      <c r="B15" s="88" t="n"/>
+      <c r="C15" s="88" t="inlineStr">
         <is>
           <t>RapidRec Tot</t>
         </is>
       </c>
-      <c r="D15" s="58" t="n"/>
-      <c r="E15" s="58" t="n"/>
-      <c r="F15" s="58" t="n"/>
-      <c r="G15" s="58" t="n"/>
-      <c r="H15" s="58" t="n"/>
-      <c r="I15" s="58" t="n"/>
-      <c r="J15" s="58" t="n"/>
-      <c r="K15" s="58" t="n"/>
-      <c r="L15" s="58" t="n"/>
-      <c r="M15" s="58" t="n"/>
-      <c r="N15" s="58" t="n"/>
-      <c r="O15" s="58" t="n"/>
-      <c r="P15" s="58" t="n"/>
-      <c r="Q15" s="58" t="n"/>
-      <c r="R15" s="58" t="n"/>
-      <c r="S15" s="58" t="n"/>
-      <c r="T15" s="58" t="n"/>
-      <c r="U15" s="58" t="n"/>
-      <c r="V15" s="58" t="n"/>
-      <c r="W15" s="58" t="n"/>
-      <c r="X15" s="58" t="n">
+      <c r="D15" s="88" t="n"/>
+      <c r="E15" s="88" t="n"/>
+      <c r="F15" s="88" t="n"/>
+      <c r="G15" s="88" t="n"/>
+      <c r="H15" s="88" t="n"/>
+      <c r="I15" s="88" t="n"/>
+      <c r="J15" s="88" t="n"/>
+      <c r="K15" s="88" t="n"/>
+      <c r="L15" s="88" t="n"/>
+      <c r="M15" s="88" t="n"/>
+      <c r="N15" s="88" t="n"/>
+      <c r="O15" s="88" t="n"/>
+      <c r="P15" s="88" t="n"/>
+      <c r="Q15" s="88" t="n"/>
+      <c r="R15" s="88" t="n"/>
+      <c r="S15" s="88" t="n"/>
+      <c r="T15" s="88" t="n"/>
+      <c r="U15" s="88" t="n"/>
+      <c r="V15" s="88" t="n"/>
+      <c r="W15" s="88" t="n"/>
+      <c r="X15" s="88" t="n">
         <v>0</v>
       </c>
-      <c r="Y15" s="58" t="n">
+      <c r="Y15" s="88" t="n">
         <v>-338</v>
       </c>
-      <c r="Z15" s="58" t="n">
+      <c r="Z15" s="88" t="n">
         <v>338</v>
       </c>
-      <c r="AA15" s="58" t="inlineStr">
+      <c r="AA15" s="88" t="inlineStr">
         <is>
           <t>RR Total</t>
         </is>
       </c>
-      <c r="AB15" s="58" t="n"/>
-      <c r="AC15" s="58" t="n"/>
+      <c r="AB15" s="88" t="n"/>
+      <c r="AC15" s="88" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="88" t="n"/>
+      <c r="B16" s="88" t="n"/>
+      <c r="C16" s="88" t="n"/>
+      <c r="D16" s="88" t="n"/>
+      <c r="E16" s="88" t="n"/>
+      <c r="F16" s="88" t="n"/>
+      <c r="G16" s="88" t="n"/>
+      <c r="H16" s="88" t="n"/>
+      <c r="I16" s="88" t="n"/>
+      <c r="J16" s="88" t="n"/>
+      <c r="K16" s="88" t="n"/>
+      <c r="L16" s="88" t="n"/>
+      <c r="M16" s="88" t="n"/>
+      <c r="N16" s="88" t="n"/>
+      <c r="O16" s="88" t="n"/>
+      <c r="P16" s="88" t="n"/>
+      <c r="Q16" s="88" t="n"/>
+      <c r="R16" s="88" t="n"/>
+      <c r="S16" s="88" t="n"/>
+      <c r="T16" s="88" t="n"/>
+      <c r="U16" s="88" t="n"/>
+      <c r="V16" s="88" t="n"/>
+      <c r="W16" s="88" t="n"/>
+      <c r="X16" s="88" t="n"/>
+      <c r="Y16" s="88" t="n"/>
+      <c r="Z16" s="88" t="n"/>
+      <c r="AA16" s="88" t="n"/>
+      <c r="AB16" s="88" t="n"/>
+      <c r="AC16" s="88" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
+      <c r="A17" s="88" t="n"/>
+      <c r="B17" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">Header Comp                             </t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="88" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="88" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="88" t="inlineStr">
         <is>
           <t>TransDate</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="88" t="inlineStr">
         <is>
           <t>GLDate</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="88" t="inlineStr">
         <is>
           <t>GLClass</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="H17" s="88" t="n"/>
+      <c r="I17" s="88" t="n"/>
+      <c r="J17" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">Doc     </t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">DT     </t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" s="88" t="inlineStr">
         <is>
           <t>OrderNum</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M17" s="88" t="inlineStr">
         <is>
           <t>OrdType</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="88" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O17" s="88" t="inlineStr">
         <is>
           <t>LineTy</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P17" s="88" t="inlineStr">
         <is>
           <t>NxtSts</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q17" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">Branch      </t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R17" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">Item                     </t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S17" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">Location            </t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T17" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">Lot                           </t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U17" s="88" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V17" s="88" t="inlineStr">
         <is>
           <t>UM</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W17" s="88" t="inlineStr">
         <is>
           <t>UnitCost</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="X17" s="88" t="n"/>
+      <c r="Y17" s="88" t="n"/>
+      <c r="Z17" s="88" t="n"/>
+      <c r="AA17" s="88" t="n"/>
+      <c r="AB17" s="88" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
+      <c r="AC17" s="88" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
+      <c r="A18" s="88" t="n"/>
+      <c r="B18" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010                                   </t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="88" t="inlineStr">
         <is>
           <t>Sales Order</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="88" t="inlineStr">
         <is>
           <t>2016-05-13</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="88" t="inlineStr">
         <is>
           <t>2016-06-09</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BRKR   </t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="H18" s="88" t="n"/>
+      <c r="I18" s="88" t="n"/>
+      <c r="J18" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">DOC-00002 </t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">RI     </t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">ORD-00001 </t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M18" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N18" s="88" t="inlineStr">
         <is>
           <t>1.000</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O18" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">W     </t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P18" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">999   </t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Q18" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">PLT3         </t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="R18" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">ITEM-00001          </t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S18" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">                    </t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T18" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">                              </t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U18" s="88" t="inlineStr">
         <is>
           <t>18.0000</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V18" s="88" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W18" s="88" t="inlineStr">
         <is>
           <t>15.3742</t>
         </is>
       </c>
-      <c r="X18" t="n">
+      <c r="X18" s="88" t="n">
         <v>276.74</v>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="Y18" s="88" t="n"/>
+      <c r="Z18" s="88" t="n"/>
+      <c r="AA18" s="88" t="n"/>
+      <c r="AB18" s="88" t="inlineStr">
         <is>
           <t>Rel order WO WO-00001 0.0000000</t>
         </is>
       </c>
+      <c r="AC18" s="88" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
+      <c r="A19" s="88" t="n"/>
+      <c r="B19" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010                                   </t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="88" t="inlineStr">
         <is>
           <t>Sales Order</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="88" t="inlineStr">
         <is>
           <t>2016-05-13</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="88" t="inlineStr">
         <is>
           <t>2016-06-06</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">FT60   </t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="H19" s="88" t="n"/>
+      <c r="I19" s="88" t="n"/>
+      <c r="J19" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">DOC-00003 </t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">RI     </t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">ORD-00001 </t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M19" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N19" s="88" t="inlineStr">
         <is>
           <t>10.000</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O19" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">F     </t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">999   </t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q19" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">PLT3         </t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="R19" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">ITEM-00002       </t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S19" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">                    </t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T19" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">                              </t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U19" s="88" t="inlineStr">
         <is>
           <t>1.0000</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V19" s="88" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W19" s="88" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="X19" t="n">
+      <c r="X19" s="88" t="n">
         <v>0</v>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="Y19" s="88" t="n"/>
+      <c r="Z19" s="88" t="n"/>
+      <c r="AA19" s="88" t="n"/>
+      <c r="AB19" s="88" t="inlineStr">
         <is>
           <t>non stock line</t>
         </is>
       </c>
+      <c r="AC19" s="88" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
+      <c r="A20" s="88" t="n"/>
+      <c r="B20" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010                                   </t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="88" t="inlineStr">
         <is>
           <t>Sales Order</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="88" t="inlineStr">
         <is>
           <t>2016-05-13</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="88" t="inlineStr">
         <is>
           <t>2016-06-09</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">FT60   </t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="H20" s="88" t="n"/>
+      <c r="I20" s="88" t="n"/>
+      <c r="J20" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">DOC-00002 </t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">RI     </t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L20" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">ORD-00001 </t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M20" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N20" s="88" t="inlineStr">
         <is>
           <t>11.000</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O20" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">F     </t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">999   </t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q20" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">PLT3         </t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R20" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">ITEM-00003       </t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S20" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">                    </t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T20" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">                              </t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U20" s="88" t="inlineStr">
         <is>
           <t>1.0000</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V20" s="88" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W20" s="88" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="X20" t="n">
+      <c r="X20" s="88" t="n">
         <v>0</v>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="Y20" s="88" t="n"/>
+      <c r="Z20" s="88" t="n"/>
+      <c r="AA20" s="88" t="n"/>
+      <c r="AB20" s="88" t="inlineStr">
         <is>
           <t>non stock line</t>
         </is>
       </c>
+      <c r="AC20" s="88" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="inlineStr">
+      <c r="A21" s="89" t="n"/>
+      <c r="B21" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">00010                                   </t>
         </is>
       </c>
-      <c r="C21" s="36" t="inlineStr">
+      <c r="C21" s="89" t="inlineStr">
         <is>
           <t>Sales Order</t>
         </is>
       </c>
-      <c r="D21" s="36" t="inlineStr">
+      <c r="D21" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="E21" s="36" t="inlineStr">
+      <c r="E21" s="89" t="inlineStr">
         <is>
           <t>2016-05-13</t>
         </is>
       </c>
-      <c r="F21" s="36" t="inlineStr">
+      <c r="F21" s="89" t="inlineStr">
         <is>
           <t>2016-08-11</t>
         </is>
       </c>
-      <c r="G21" s="36" t="inlineStr">
+      <c r="G21" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">BUYP   </t>
         </is>
       </c>
-      <c r="H21" s="36" t="n"/>
-      <c r="I21" s="36" t="n"/>
-      <c r="J21" s="36" t="inlineStr">
+      <c r="H21" s="89" t="n"/>
+      <c r="I21" s="89" t="n"/>
+      <c r="J21" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">DOC-00001 </t>
         </is>
       </c>
-      <c r="K21" s="36" t="inlineStr">
+      <c r="K21" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">RI     </t>
         </is>
       </c>
-      <c r="L21" s="36" t="inlineStr">
+      <c r="L21" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">ORD-00001 </t>
         </is>
       </c>
-      <c r="M21" s="36" t="inlineStr">
+      <c r="M21" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="N21" s="36" t="inlineStr">
+      <c r="N21" s="89" t="inlineStr">
         <is>
           <t>13.000</t>
         </is>
       </c>
-      <c r="O21" s="36" t="inlineStr">
+      <c r="O21" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">N     </t>
         </is>
       </c>
-      <c r="P21" s="36" t="inlineStr">
+      <c r="P21" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">999   </t>
         </is>
       </c>
-      <c r="Q21" s="36" t="inlineStr">
+      <c r="Q21" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">PLT2         </t>
         </is>
       </c>
-      <c r="R21" s="36" t="inlineStr">
+      <c r="R21" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">ITEM-00004                  </t>
         </is>
       </c>
-      <c r="S21" s="36" t="inlineStr">
+      <c r="S21" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">                    </t>
         </is>
       </c>
-      <c r="T21" s="36" t="inlineStr">
+      <c r="T21" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">                              </t>
         </is>
       </c>
-      <c r="U21" s="36" t="inlineStr">
+      <c r="U21" s="89" t="inlineStr">
         <is>
           <t>1000.0000</t>
         </is>
       </c>
-      <c r="V21" s="36" t="inlineStr">
+      <c r="V21" s="89" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="W21" s="36" t="inlineStr">
+      <c r="W21" s="89" t="inlineStr">
         <is>
           <t>0.3380</t>
         </is>
       </c>
-      <c r="X21" s="36" t="n">
+      <c r="X21" s="89" t="n">
         <v>338</v>
       </c>
-      <c r="Y21" s="36" t="n"/>
-      <c r="Z21" s="36" t="n"/>
-      <c r="AA21" s="36" t="n"/>
-      <c r="AB21" s="36" t="inlineStr">
+      <c r="Y21" s="89" t="n"/>
+      <c r="Z21" s="89" t="n"/>
+      <c r="AA21" s="89" t="n"/>
+      <c r="AB21" s="89" t="inlineStr">
         <is>
           <t>non stock line</t>
         </is>
       </c>
-      <c r="AC21" s="36" t="n"/>
+      <c r="AC21" s="89" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr">
+      <c r="A22" s="88" t="n"/>
+      <c r="B22" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010                                   </t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="88" t="inlineStr">
         <is>
           <t>Sales Order</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="88" t="inlineStr">
         <is>
           <t>2016-05-13</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="88" t="inlineStr">
         <is>
           <t>2016-05-16</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BUYP   </t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="H22" s="88" t="n"/>
+      <c r="I22" s="88" t="n"/>
+      <c r="J22" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">DOC-00005 </t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">RI     </t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L22" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">ORD-00001 </t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M22" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N22" s="88" t="inlineStr">
         <is>
           <t>2.000</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O22" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">S     </t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P22" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">999   </t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q22" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">PLT1         </t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R22" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">ITEM-00004                  </t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S22" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">                    </t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T22" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">                              </t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U22" s="88" t="inlineStr">
         <is>
           <t>1000.0000</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V22" s="88" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W22" s="88" t="inlineStr">
         <is>
           <t>0.3380</t>
         </is>
       </c>
-      <c r="X22" t="n">
+      <c r="X22" s="88" t="n">
         <v>338</v>
       </c>
+      <c r="Y22" s="88" t="n"/>
+      <c r="Z22" s="88" t="n"/>
+      <c r="AA22" s="88" t="n"/>
+      <c r="AB22" s="88" t="n"/>
+      <c r="AC22" s="88" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
+      <c r="A23" s="88" t="n"/>
+      <c r="B23" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010                                   </t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="88" t="inlineStr">
         <is>
           <t>Sales Order</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="88" t="inlineStr">
         <is>
           <t>2016-05-13</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="88" t="inlineStr">
         <is>
           <t>2016-07-29</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BUYP   </t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="H23" s="88" t="n"/>
+      <c r="I23" s="88" t="n"/>
+      <c r="J23" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">DOC-00004 </t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">RI     </t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L23" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">ORD-00001 </t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M23" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N23" s="88" t="inlineStr">
         <is>
           <t>3.000</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O23" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">S     </t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P23" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">999   </t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q23" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">PLT1         </t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="R23" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">ITEM-00004                  </t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S23" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">                    </t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T23" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">                              </t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U23" s="88" t="inlineStr">
         <is>
           <t>1000.0000</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V23" s="88" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W23" s="88" t="inlineStr">
         <is>
           <t>0.3380</t>
         </is>
       </c>
-      <c r="X23" t="n">
+      <c r="X23" s="88" t="n">
         <v>338</v>
       </c>
+      <c r="Y23" s="88" t="n"/>
+      <c r="Z23" s="88" t="n"/>
+      <c r="AA23" s="88" t="n"/>
+      <c r="AB23" s="88" t="n"/>
+      <c r="AC23" s="88" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="36" t="n"/>
-      <c r="B24" s="36" t="inlineStr">
+      <c r="A24" s="90" t="n"/>
+      <c r="B24" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">00010                                   </t>
         </is>
       </c>
-      <c r="C24" s="36" t="inlineStr">
+      <c r="C24" s="90" t="inlineStr">
         <is>
           <t>Sales Order</t>
         </is>
       </c>
-      <c r="D24" s="36" t="inlineStr">
+      <c r="D24" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="E24" s="36" t="inlineStr">
+      <c r="E24" s="90" t="inlineStr">
         <is>
           <t>2016-05-13</t>
         </is>
       </c>
-      <c r="F24" s="36" t="inlineStr">
+      <c r="F24" s="90" t="inlineStr">
         <is>
           <t>2000-01-01</t>
         </is>
       </c>
-      <c r="G24" s="36" t="inlineStr">
+      <c r="G24" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">BUYP   </t>
         </is>
       </c>
-      <c r="H24" s="36" t="n"/>
-      <c r="I24" s="36" t="n"/>
-      <c r="J24" s="36" t="inlineStr">
+      <c r="H24" s="90" t="n"/>
+      <c r="I24" s="90" t="n"/>
+      <c r="J24" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">0       </t>
         </is>
       </c>
-      <c r="K24" s="36" t="inlineStr">
+      <c r="K24" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
       </c>
-      <c r="L24" s="36" t="inlineStr">
+      <c r="L24" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">ORD-00001 </t>
         </is>
       </c>
-      <c r="M24" s="36" t="inlineStr">
+      <c r="M24" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="N24" s="36" t="inlineStr">
+      <c r="N24" s="90" t="inlineStr">
         <is>
           <t>4.000</t>
         </is>
       </c>
-      <c r="O24" s="36" t="inlineStr">
+      <c r="O24" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">S     </t>
         </is>
       </c>
-      <c r="P24" s="36" t="inlineStr">
+      <c r="P24" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">999   </t>
         </is>
       </c>
-      <c r="Q24" s="36" t="inlineStr">
+      <c r="Q24" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">PLT1         </t>
         </is>
       </c>
-      <c r="R24" s="36" t="inlineStr">
+      <c r="R24" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">ITEM-00004                  </t>
         </is>
       </c>
-      <c r="S24" s="36" t="inlineStr">
+      <c r="S24" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">                    </t>
         </is>
       </c>
-      <c r="T24" s="36" t="inlineStr">
+      <c r="T24" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">                              </t>
         </is>
       </c>
-      <c r="U24" s="36" t="inlineStr">
+      <c r="U24" s="90" t="inlineStr">
         <is>
           <t>1000.0000</t>
         </is>
       </c>
-      <c r="V24" s="36" t="inlineStr">
+      <c r="V24" s="90" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="W24" s="36" t="inlineStr">
+      <c r="W24" s="90" t="inlineStr">
         <is>
           <t>0.3380</t>
         </is>
       </c>
-      <c r="X24" s="36" t="n">
+      <c r="X24" s="90" t="n">
         <v>0</v>
       </c>
-      <c r="Y24" s="36" t="n"/>
-      <c r="Z24" s="36" t="n"/>
-      <c r="AA24" s="36" t="n"/>
-      <c r="AB24" s="36" t="inlineStr">
+      <c r="Y24" s="90" t="n"/>
+      <c r="Z24" s="90" t="n"/>
+      <c r="AA24" s="90" t="n"/>
+      <c r="AB24" s="90" t="inlineStr">
         <is>
           <t>sales ext cost error calc = 338.0000</t>
         </is>
       </c>
-      <c r="AC24" s="36" t="n"/>
+      <c r="AC24" s="90" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
+      <c r="A25" s="88" t="n"/>
+      <c r="B25" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010                                   </t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="88" t="inlineStr">
         <is>
           <t>Sales Order</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="88" t="inlineStr">
         <is>
           <t>2016-05-13</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="88" t="inlineStr">
         <is>
           <t>2016-06-02</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SWIT   </t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="H25" s="88" t="n"/>
+      <c r="I25" s="88" t="n"/>
+      <c r="J25" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">DOC-00006 </t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">RI     </t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L25" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">ORD-00001 </t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M25" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N25" s="88" t="inlineStr">
         <is>
           <t>5.000</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O25" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">W     </t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P25" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">999   </t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q25" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">PLT3         </t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R25" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">ITEM-00005             </t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S25" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">                    </t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T25" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">                              </t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U25" s="88" t="inlineStr">
         <is>
           <t>250.0000</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V25" s="88" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W25" s="88" t="inlineStr">
         <is>
           <t>0.2373</t>
         </is>
       </c>
-      <c r="X25" t="n">
+      <c r="X25" s="88" t="n">
         <v>59.33</v>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="Y25" s="88" t="n"/>
+      <c r="Z25" s="88" t="n"/>
+      <c r="AA25" s="88" t="n"/>
+      <c r="AB25" s="88" t="inlineStr">
         <is>
           <t>Rel order WO WO-00002 0.0000000</t>
         </is>
       </c>
+      <c r="AC25" s="88" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
+      <c r="A26" s="88" t="n"/>
+      <c r="B26" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010                                   </t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="88" t="inlineStr">
         <is>
           <t>Sales Order</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="88" t="inlineStr">
         <is>
           <t>2016-05-13</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="88" t="inlineStr">
         <is>
           <t>2016-06-06</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SWIT   </t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="H26" s="88" t="n"/>
+      <c r="I26" s="88" t="n"/>
+      <c r="J26" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">DOC-00003 </t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">RI     </t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L26" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">ORD-00001 </t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M26" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N26" s="88" t="inlineStr">
         <is>
           <t>6.000</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O26" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">W     </t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P26" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">999   </t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q26" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">PLT3         </t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="R26" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">ITEM-00006              </t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S26" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">                    </t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T26" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">                              </t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U26" s="88" t="inlineStr">
         <is>
           <t>200.0000</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V26" s="88" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W26" s="88" t="inlineStr">
         <is>
           <t>0.2583</t>
         </is>
       </c>
-      <c r="X26" t="n">
+      <c r="X26" s="88" t="n">
         <v>51.66</v>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="Y26" s="88" t="n"/>
+      <c r="Z26" s="88" t="n"/>
+      <c r="AA26" s="88" t="n"/>
+      <c r="AB26" s="88" t="inlineStr">
         <is>
           <t>Rel order WO WO-00003 0.0000000</t>
         </is>
       </c>
+      <c r="AC26" s="88" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
+      <c r="A27" s="88" t="n"/>
+      <c r="B27" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010                                   </t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="88" t="inlineStr">
         <is>
           <t>Sales Order</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="88" t="inlineStr">
         <is>
           <t>2016-05-13</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="88" t="inlineStr">
         <is>
           <t>2000-01-01</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SWIT   </t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="H27" s="88" t="n"/>
+      <c r="I27" s="88" t="n"/>
+      <c r="J27" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">0       </t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L27" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">ORD-00001 </t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M27" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N27" s="88" t="inlineStr">
         <is>
           <t>7.000</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O27" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">W     </t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P27" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">999   </t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q27" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">PLT3         </t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="R27" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">ITEM-00006              </t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S27" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">                    </t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T27" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">                              </t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U27" s="88" t="inlineStr">
         <is>
           <t>100.0000</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V27" s="88" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W27" s="88" t="inlineStr">
         <is>
           <t>0.2583</t>
         </is>
       </c>
-      <c r="X27" t="n">
+      <c r="X27" s="88" t="n">
         <v>0</v>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="Y27" s="88" t="n"/>
+      <c r="Z27" s="88" t="n"/>
+      <c r="AA27" s="88" t="n"/>
+      <c r="AB27" s="88" t="inlineStr">
         <is>
           <t>Rel order WO WO-00004 0.0000000</t>
         </is>
       </c>
+      <c r="AC27" s="88" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
+      <c r="A28" s="88" t="n"/>
+      <c r="B28" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010                                   </t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="88" t="inlineStr">
         <is>
           <t>Sales Order</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="88" t="inlineStr">
         <is>
           <t>2016-05-13</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="88" t="inlineStr">
         <is>
           <t>2016-05-16</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">FT60   </t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="H28" s="88" t="n"/>
+      <c r="I28" s="88" t="n"/>
+      <c r="J28" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">DOC-00005 </t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">RI     </t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L28" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">ORD-00001 </t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M28" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N28" s="88" t="inlineStr">
         <is>
           <t>8.000</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O28" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">F     </t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P28" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">999   </t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q28" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">PLT3         </t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R28" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">ITEM-00007       </t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S28" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">                    </t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T28" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">                              </t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U28" s="88" t="inlineStr">
         <is>
           <t>1.0000</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V28" s="88" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W28" s="88" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="X28" t="n">
+      <c r="X28" s="88" t="n">
         <v>0</v>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="Y28" s="88" t="n"/>
+      <c r="Z28" s="88" t="n"/>
+      <c r="AA28" s="88" t="n"/>
+      <c r="AB28" s="88" t="inlineStr">
         <is>
           <t>non stock line</t>
         </is>
       </c>
+      <c r="AC28" s="88" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
+      <c r="A29" s="88" t="n"/>
+      <c r="B29" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010                                   </t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="88" t="inlineStr">
         <is>
           <t>Sales Order</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="88" t="inlineStr">
         <is>
           <t>2016-05-13</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="88" t="inlineStr">
         <is>
           <t>2016-06-02</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">FT60   </t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="H29" s="88" t="n"/>
+      <c r="I29" s="88" t="n"/>
+      <c r="J29" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">DOC-00006 </t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K29" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">RI     </t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L29" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">ORD-00001 </t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M29" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N29" s="88" t="inlineStr">
         <is>
           <t>9.000</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O29" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">F     </t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P29" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">999   </t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q29" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">PLT3         </t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R29" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">ITEM-00008       </t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S29" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">                    </t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T29" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">                              </t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U29" s="88" t="inlineStr">
         <is>
           <t>1.0000</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V29" s="88" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W29" s="88" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="X29" t="n">
+      <c r="X29" s="88" t="n">
         <v>0</v>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="Y29" s="88" t="n"/>
+      <c r="Z29" s="88" t="n"/>
+      <c r="AA29" s="88" t="n"/>
+      <c r="AB29" s="88" t="inlineStr">
         <is>
           <t>non stock line</t>
         </is>
       </c>
+      <c r="AC29" s="88" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="88" t="n"/>
+      <c r="B30" s="88" t="n"/>
+      <c r="C30" s="88" t="n"/>
+      <c r="D30" s="88" t="n"/>
+      <c r="E30" s="88" t="n"/>
+      <c r="F30" s="88" t="n"/>
+      <c r="G30" s="88" t="n"/>
+      <c r="H30" s="88" t="n"/>
+      <c r="I30" s="88" t="n"/>
+      <c r="J30" s="88" t="n"/>
+      <c r="K30" s="88" t="n"/>
+      <c r="L30" s="88" t="n"/>
+      <c r="M30" s="88" t="n"/>
+      <c r="N30" s="88" t="n"/>
+      <c r="O30" s="88" t="n"/>
+      <c r="P30" s="88" t="n"/>
+      <c r="Q30" s="88" t="n"/>
+      <c r="R30" s="88" t="n"/>
+      <c r="S30" s="88" t="n"/>
+      <c r="T30" s="88" t="n"/>
+      <c r="U30" s="88" t="n"/>
+      <c r="V30" s="88" t="n"/>
+      <c r="W30" s="88" t="n"/>
+      <c r="X30" s="88" t="n"/>
+      <c r="Y30" s="88" t="n"/>
+      <c r="Z30" s="88" t="n"/>
+      <c r="AA30" s="88" t="n"/>
+      <c r="AB30" s="88" t="n"/>
+      <c r="AC30" s="88" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
+      <c r="A31" s="88" t="n"/>
+      <c r="B31" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">DMAAIs                                  </t>
         </is>
       </c>
+      <c r="C31" s="88" t="n"/>
+      <c r="D31" s="88" t="n"/>
+      <c r="E31" s="88" t="n"/>
+      <c r="F31" s="88" t="n"/>
+      <c r="G31" s="88" t="n"/>
+      <c r="H31" s="88" t="n"/>
+      <c r="I31" s="88" t="n"/>
+      <c r="J31" s="88" t="n"/>
+      <c r="K31" s="88" t="n"/>
+      <c r="L31" s="88" t="n"/>
+      <c r="M31" s="88" t="n"/>
+      <c r="N31" s="88" t="n"/>
+      <c r="O31" s="88" t="n"/>
+      <c r="P31" s="88" t="n"/>
+      <c r="Q31" s="88" t="n"/>
+      <c r="R31" s="88" t="n"/>
+      <c r="S31" s="88" t="n"/>
+      <c r="T31" s="88" t="n"/>
+      <c r="U31" s="88" t="n"/>
+      <c r="V31" s="88" t="n"/>
+      <c r="W31" s="88" t="n"/>
+      <c r="X31" s="88" t="n"/>
+      <c r="Y31" s="88" t="n"/>
+      <c r="Z31" s="88" t="n"/>
+      <c r="AA31" s="88" t="n"/>
+      <c r="AB31" s="88" t="n"/>
+      <c r="AC31" s="88" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr">
+      <c r="A32" s="88" t="n"/>
+      <c r="B32" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">Model Account                           </t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="88" t="inlineStr">
         <is>
           <t>DMAAI Table</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="88" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="E32" s="88" t="n"/>
+      <c r="F32" s="88" t="n"/>
+      <c r="G32" s="88" t="inlineStr">
         <is>
           <t>GLClass</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="H32" s="88" t="n"/>
+      <c r="I32" s="88" t="n"/>
+      <c r="J32" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">Object  </t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">Ty     </t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="L32" s="88" t="n"/>
+      <c r="M32" s="88" t="n"/>
+      <c r="N32" s="88" t="n"/>
+      <c r="O32" s="88" t="n"/>
+      <c r="P32" s="88" t="n"/>
+      <c r="Q32" s="88" t="n"/>
+      <c r="R32" s="88" t="n"/>
+      <c r="S32" s="88" t="n"/>
+      <c r="T32" s="88" t="n"/>
+      <c r="U32" s="88" t="n"/>
+      <c r="V32" s="88" t="n"/>
+      <c r="W32" s="88" t="n"/>
+      <c r="X32" s="88" t="n"/>
+      <c r="Y32" s="88" t="n"/>
+      <c r="Z32" s="88" t="n"/>
+      <c r="AA32" s="88" t="n"/>
+      <c r="AB32" s="88" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
+      <c r="AC32" s="88" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr">
+      <c r="A33" s="88" t="n"/>
+      <c r="B33" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BU1.145000                          </t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="88" t="inlineStr">
         <is>
           <t>4152 Inv Model</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="E33" s="88" t="n"/>
+      <c r="F33" s="88" t="n"/>
+      <c r="G33" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BRKR   </t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="H33" s="88" t="n"/>
+      <c r="I33" s="88" t="n"/>
+      <c r="J33" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">145000  </t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">99     </t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="L33" s="88" t="n"/>
+      <c r="M33" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
       </c>
+      <c r="N33" s="88" t="n"/>
+      <c r="O33" s="88" t="n"/>
+      <c r="P33" s="88" t="n"/>
+      <c r="Q33" s="88" t="n"/>
+      <c r="R33" s="88" t="n"/>
+      <c r="S33" s="88" t="n"/>
+      <c r="T33" s="88" t="n"/>
+      <c r="U33" s="88" t="n"/>
+      <c r="V33" s="88" t="n"/>
+      <c r="W33" s="88" t="n"/>
+      <c r="X33" s="88" t="n"/>
+      <c r="Y33" s="88" t="n"/>
+      <c r="Z33" s="88" t="n"/>
+      <c r="AA33" s="88" t="n"/>
+      <c r="AB33" s="88" t="n"/>
+      <c r="AC33" s="88" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr">
+      <c r="A34" s="88" t="n"/>
+      <c r="B34" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BU1.142000                          </t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="88" t="inlineStr">
         <is>
           <t>4152 Inv Model</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="E34" s="88" t="n"/>
+      <c r="F34" s="88" t="n"/>
+      <c r="G34" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BUYP   </t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="H34" s="88" t="n"/>
+      <c r="I34" s="88" t="n"/>
+      <c r="J34" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">142000  </t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">99     </t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="L34" s="88" t="n"/>
+      <c r="M34" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
       </c>
+      <c r="N34" s="88" t="n"/>
+      <c r="O34" s="88" t="n"/>
+      <c r="P34" s="88" t="n"/>
+      <c r="Q34" s="88" t="n"/>
+      <c r="R34" s="88" t="n"/>
+      <c r="S34" s="88" t="n"/>
+      <c r="T34" s="88" t="n"/>
+      <c r="U34" s="88" t="n"/>
+      <c r="V34" s="88" t="n"/>
+      <c r="W34" s="88" t="n"/>
+      <c r="X34" s="88" t="n"/>
+      <c r="Y34" s="88" t="n"/>
+      <c r="Z34" s="88" t="n"/>
+      <c r="AA34" s="88" t="n"/>
+      <c r="AB34" s="88" t="n"/>
+      <c r="AC34" s="88" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr">
+      <c r="A35" s="87" t="n"/>
+      <c r="B35" s="87" t="inlineStr">
         <is>
           <t xml:space="preserve">Missing entry                           </t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="87" t="inlineStr">
         <is>
           <t>4152 Inv Model</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="87" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="87" t="inlineStr">
         <is>
           <t>Invalid Acct</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="F35" s="87" t="n"/>
+      <c r="G35" s="87" t="inlineStr">
         <is>
           <t xml:space="preserve">FT60   </t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="H35" s="87" t="n"/>
+      <c r="I35" s="87" t="n"/>
+      <c r="J35" s="87" t="inlineStr">
         <is>
           <t xml:space="preserve">None    </t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="K35" s="87" t="n"/>
+      <c r="L35" s="87" t="n"/>
+      <c r="M35" s="87" t="n"/>
+      <c r="N35" s="87" t="n"/>
+      <c r="O35" s="87" t="n"/>
+      <c r="P35" s="87" t="n"/>
+      <c r="Q35" s="87" t="n"/>
+      <c r="R35" s="87" t="n"/>
+      <c r="S35" s="87" t="n"/>
+      <c r="T35" s="87" t="n"/>
+      <c r="U35" s="87" t="n"/>
+      <c r="V35" s="87" t="n"/>
+      <c r="W35" s="87" t="n"/>
+      <c r="X35" s="87" t="n"/>
+      <c r="Y35" s="87" t="n"/>
+      <c r="Z35" s="87" t="n"/>
+      <c r="AA35" s="87" t="n"/>
+      <c r="AB35" s="87" t="inlineStr">
         <is>
           <t>Missing model table entry</t>
         </is>
       </c>
+      <c r="AC35" s="87" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr">
+      <c r="A36" s="88" t="n"/>
+      <c r="B36" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BU1.145000                          </t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="88" t="inlineStr">
         <is>
           <t>4152 Inv Model</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="E36" s="88" t="n"/>
+      <c r="F36" s="88" t="n"/>
+      <c r="G36" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SWIT   </t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="H36" s="88" t="n"/>
+      <c r="I36" s="88" t="n"/>
+      <c r="J36" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">145000  </t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K36" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">99     </t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="L36" s="88" t="n"/>
+      <c r="M36" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
       </c>
+      <c r="N36" s="88" t="n"/>
+      <c r="O36" s="88" t="n"/>
+      <c r="P36" s="88" t="n"/>
+      <c r="Q36" s="88" t="n"/>
+      <c r="R36" s="88" t="n"/>
+      <c r="S36" s="88" t="n"/>
+      <c r="T36" s="88" t="n"/>
+      <c r="U36" s="88" t="n"/>
+      <c r="V36" s="88" t="n"/>
+      <c r="W36" s="88" t="n"/>
+      <c r="X36" s="88" t="n"/>
+      <c r="Y36" s="88" t="n"/>
+      <c r="Z36" s="88" t="n"/>
+      <c r="AA36" s="88" t="n"/>
+      <c r="AB36" s="88" t="n"/>
+      <c r="AC36" s="88" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="88" t="n"/>
+      <c r="B37" s="88" t="n"/>
+      <c r="C37" s="88" t="n"/>
+      <c r="D37" s="88" t="n"/>
+      <c r="E37" s="88" t="n"/>
+      <c r="F37" s="88" t="n"/>
+      <c r="G37" s="88" t="n"/>
+      <c r="H37" s="88" t="n"/>
+      <c r="I37" s="88" t="n"/>
+      <c r="J37" s="88" t="n"/>
+      <c r="K37" s="88" t="n"/>
+      <c r="L37" s="88" t="n"/>
+      <c r="M37" s="88" t="n"/>
+      <c r="N37" s="88" t="n"/>
+      <c r="O37" s="88" t="n"/>
+      <c r="P37" s="88" t="n"/>
+      <c r="Q37" s="88" t="n"/>
+      <c r="R37" s="88" t="n"/>
+      <c r="S37" s="88" t="n"/>
+      <c r="T37" s="88" t="n"/>
+      <c r="U37" s="88" t="n"/>
+      <c r="V37" s="88" t="n"/>
+      <c r="W37" s="88" t="n"/>
+      <c r="X37" s="88" t="n"/>
+      <c r="Y37" s="88" t="n"/>
+      <c r="Z37" s="88" t="n"/>
+      <c r="AA37" s="88" t="n"/>
+      <c r="AB37" s="88" t="n"/>
+      <c r="AC37" s="88" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr">
+      <c r="A38" s="88" t="n"/>
+      <c r="B38" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">Inv Account                             </t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="88" t="inlineStr">
         <is>
           <t>DMAAI Table</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="88" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="E38" s="88" t="n"/>
+      <c r="F38" s="88" t="n"/>
+      <c r="G38" s="88" t="inlineStr">
         <is>
           <t>GLClass</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="H38" s="88" t="n"/>
+      <c r="I38" s="88" t="n"/>
+      <c r="J38" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">Object  </t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K38" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">Ty     </t>
         </is>
       </c>
+      <c r="L38" s="88" t="n"/>
+      <c r="M38" s="88" t="n"/>
+      <c r="N38" s="88" t="n"/>
+      <c r="O38" s="88" t="n"/>
+      <c r="P38" s="88" t="n"/>
+      <c r="Q38" s="88" t="n"/>
+      <c r="R38" s="88" t="n"/>
+      <c r="S38" s="88" t="n"/>
+      <c r="T38" s="88" t="n"/>
+      <c r="U38" s="88" t="n"/>
+      <c r="V38" s="88" t="n"/>
+      <c r="W38" s="88" t="n"/>
+      <c r="X38" s="88" t="n"/>
+      <c r="Y38" s="88" t="n"/>
+      <c r="Z38" s="88" t="n"/>
+      <c r="AA38" s="88" t="n"/>
+      <c r="AB38" s="88" t="n"/>
+      <c r="AC38" s="88" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr">
+      <c r="A39" s="88" t="n"/>
+      <c r="B39" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BU1.145000                          </t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="88" t="inlineStr">
         <is>
           <t>4240 Inv Sales</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="E39" s="88" t="n"/>
+      <c r="F39" s="88" t="n"/>
+      <c r="G39" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BRKR   </t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="H39" s="88" t="n"/>
+      <c r="I39" s="88" t="n"/>
+      <c r="J39" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">145000  </t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K39" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="L39" s="88" t="n"/>
+      <c r="M39" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
       </c>
+      <c r="N39" s="88" t="n"/>
+      <c r="O39" s="88" t="n"/>
+      <c r="P39" s="88" t="n"/>
+      <c r="Q39" s="88" t="n"/>
+      <c r="R39" s="88" t="n"/>
+      <c r="S39" s="88" t="n"/>
+      <c r="T39" s="88" t="n"/>
+      <c r="U39" s="88" t="n"/>
+      <c r="V39" s="88" t="n"/>
+      <c r="W39" s="88" t="n"/>
+      <c r="X39" s="88" t="n"/>
+      <c r="Y39" s="88" t="n"/>
+      <c r="Z39" s="88" t="n"/>
+      <c r="AA39" s="88" t="n"/>
+      <c r="AB39" s="88" t="n"/>
+      <c r="AC39" s="88" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr">
+      <c r="A40" s="88" t="n"/>
+      <c r="B40" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BU1.142000                          </t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="88" t="inlineStr">
         <is>
           <t>4240 Inv Sales</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="E40" s="88" t="n"/>
+      <c r="F40" s="88" t="n"/>
+      <c r="G40" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BUYP   </t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="H40" s="88" t="n"/>
+      <c r="I40" s="88" t="n"/>
+      <c r="J40" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">142000  </t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K40" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="L40" s="88" t="n"/>
+      <c r="M40" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
       </c>
+      <c r="N40" s="88" t="n"/>
+      <c r="O40" s="88" t="n"/>
+      <c r="P40" s="88" t="n"/>
+      <c r="Q40" s="88" t="n"/>
+      <c r="R40" s="88" t="n"/>
+      <c r="S40" s="88" t="n"/>
+      <c r="T40" s="88" t="n"/>
+      <c r="U40" s="88" t="n"/>
+      <c r="V40" s="88" t="n"/>
+      <c r="W40" s="88" t="n"/>
+      <c r="X40" s="88" t="n"/>
+      <c r="Y40" s="88" t="n"/>
+      <c r="Z40" s="88" t="n"/>
+      <c r="AA40" s="88" t="n"/>
+      <c r="AB40" s="88" t="n"/>
+      <c r="AC40" s="88" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr">
+      <c r="A41" s="88" t="n"/>
+      <c r="B41" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BU1.145000                          </t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="88" t="inlineStr">
         <is>
           <t>4240 Inv Sales</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="E41" s="88" t="n"/>
+      <c r="F41" s="88" t="n"/>
+      <c r="G41" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SWIT   </t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="H41" s="88" t="n"/>
+      <c r="I41" s="88" t="n"/>
+      <c r="J41" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">145000  </t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K41" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="L41" s="88" t="n"/>
+      <c r="M41" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
       </c>
+      <c r="N41" s="88" t="n"/>
+      <c r="O41" s="88" t="n"/>
+      <c r="P41" s="88" t="n"/>
+      <c r="Q41" s="88" t="n"/>
+      <c r="R41" s="88" t="n"/>
+      <c r="S41" s="88" t="n"/>
+      <c r="T41" s="88" t="n"/>
+      <c r="U41" s="88" t="n"/>
+      <c r="V41" s="88" t="n"/>
+      <c r="W41" s="88" t="n"/>
+      <c r="X41" s="88" t="n"/>
+      <c r="Y41" s="88" t="n"/>
+      <c r="Z41" s="88" t="n"/>
+      <c r="AA41" s="88" t="n"/>
+      <c r="AB41" s="88" t="n"/>
+      <c r="AC41" s="88" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="88" t="n"/>
+      <c r="B42" s="88" t="n"/>
+      <c r="C42" s="88" t="n"/>
+      <c r="D42" s="88" t="n"/>
+      <c r="E42" s="88" t="n"/>
+      <c r="F42" s="88" t="n"/>
+      <c r="G42" s="88" t="n"/>
+      <c r="H42" s="88" t="n"/>
+      <c r="I42" s="88" t="n"/>
+      <c r="J42" s="88" t="n"/>
+      <c r="K42" s="88" t="n"/>
+      <c r="L42" s="88" t="n"/>
+      <c r="M42" s="88" t="n"/>
+      <c r="N42" s="88" t="n"/>
+      <c r="O42" s="88" t="n"/>
+      <c r="P42" s="88" t="n"/>
+      <c r="Q42" s="88" t="n"/>
+      <c r="R42" s="88" t="n"/>
+      <c r="S42" s="88" t="n"/>
+      <c r="T42" s="88" t="n"/>
+      <c r="U42" s="88" t="n"/>
+      <c r="V42" s="88" t="n"/>
+      <c r="W42" s="88" t="n"/>
+      <c r="X42" s="88" t="n"/>
+      <c r="Y42" s="88" t="n"/>
+      <c r="Z42" s="88" t="n"/>
+      <c r="AA42" s="88" t="n"/>
+      <c r="AB42" s="88" t="n"/>
+      <c r="AC42" s="88" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr">
+      <c r="A43" s="88" t="n"/>
+      <c r="B43" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">Exp Account                             </t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="88" t="inlineStr">
         <is>
           <t>DMAAI Table</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="88" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="E43" s="88" t="n"/>
+      <c r="F43" s="88" t="n"/>
+      <c r="G43" s="88" t="inlineStr">
         <is>
           <t>GLClass</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="H43" s="88" t="n"/>
+      <c r="I43" s="88" t="n"/>
+      <c r="J43" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">Object  </t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">Ty     </t>
         </is>
       </c>
+      <c r="L43" s="88" t="n"/>
+      <c r="M43" s="88" t="n"/>
+      <c r="N43" s="88" t="n"/>
+      <c r="O43" s="88" t="n"/>
+      <c r="P43" s="88" t="n"/>
+      <c r="Q43" s="88" t="n"/>
+      <c r="R43" s="88" t="n"/>
+      <c r="S43" s="88" t="n"/>
+      <c r="T43" s="88" t="n"/>
+      <c r="U43" s="88" t="n"/>
+      <c r="V43" s="88" t="n"/>
+      <c r="W43" s="88" t="n"/>
+      <c r="X43" s="88" t="n"/>
+      <c r="Y43" s="88" t="n"/>
+      <c r="Z43" s="88" t="n"/>
+      <c r="AA43" s="88" t="n"/>
+      <c r="AB43" s="88" t="n"/>
+      <c r="AC43" s="88" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr">
+      <c r="A44" s="88" t="n"/>
+      <c r="B44" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BU2.501010                          </t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="88" t="inlineStr">
         <is>
           <t>4141 Exp St Cst Var</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="E44" s="88" t="n"/>
+      <c r="F44" s="88" t="n"/>
+      <c r="G44" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BRKR   </t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="H44" s="88" t="n"/>
+      <c r="I44" s="88" t="n"/>
+      <c r="J44" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">501010  </t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K44" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="L44" s="88" t="n"/>
+      <c r="M44" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
       </c>
+      <c r="N44" s="88" t="n"/>
+      <c r="O44" s="88" t="n"/>
+      <c r="P44" s="88" t="n"/>
+      <c r="Q44" s="88" t="n"/>
+      <c r="R44" s="88" t="n"/>
+      <c r="S44" s="88" t="n"/>
+      <c r="T44" s="88" t="n"/>
+      <c r="U44" s="88" t="n"/>
+      <c r="V44" s="88" t="n"/>
+      <c r="W44" s="88" t="n"/>
+      <c r="X44" s="88" t="n"/>
+      <c r="Y44" s="88" t="n"/>
+      <c r="Z44" s="88" t="n"/>
+      <c r="AA44" s="88" t="n"/>
+      <c r="AB44" s="88" t="n"/>
+      <c r="AC44" s="88" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr">
+      <c r="A45" s="88" t="n"/>
+      <c r="B45" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BU2.501010                          </t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="88" t="inlineStr">
         <is>
           <t>4220 COGS</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="E45" s="88" t="n"/>
+      <c r="F45" s="88" t="n"/>
+      <c r="G45" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BRKR   </t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="H45" s="88" t="n"/>
+      <c r="I45" s="88" t="n"/>
+      <c r="J45" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">501010  </t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="L45" s="88" t="n"/>
+      <c r="M45" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
       </c>
+      <c r="N45" s="88" t="n"/>
+      <c r="O45" s="88" t="n"/>
+      <c r="P45" s="88" t="n"/>
+      <c r="Q45" s="88" t="n"/>
+      <c r="R45" s="88" t="n"/>
+      <c r="S45" s="88" t="n"/>
+      <c r="T45" s="88" t="n"/>
+      <c r="U45" s="88" t="n"/>
+      <c r="V45" s="88" t="n"/>
+      <c r="W45" s="88" t="n"/>
+      <c r="X45" s="88" t="n"/>
+      <c r="Y45" s="88" t="n"/>
+      <c r="Z45" s="88" t="n"/>
+      <c r="AA45" s="88" t="n"/>
+      <c r="AB45" s="88" t="n"/>
+      <c r="AC45" s="88" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr">
+      <c r="A46" s="88" t="n"/>
+      <c r="B46" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BU3.401022                          </t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="88" t="inlineStr">
         <is>
           <t>4230 Revenue</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="E46" s="88" t="n"/>
+      <c r="F46" s="88" t="n"/>
+      <c r="G46" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BRKR   </t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="H46" s="88" t="n"/>
+      <c r="I46" s="88" t="n"/>
+      <c r="J46" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">401022  </t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K46" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="L46" s="88" t="n"/>
+      <c r="M46" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
       </c>
+      <c r="N46" s="88" t="n"/>
+      <c r="O46" s="88" t="n"/>
+      <c r="P46" s="88" t="n"/>
+      <c r="Q46" s="88" t="n"/>
+      <c r="R46" s="88" t="n"/>
+      <c r="S46" s="88" t="n"/>
+      <c r="T46" s="88" t="n"/>
+      <c r="U46" s="88" t="n"/>
+      <c r="V46" s="88" t="n"/>
+      <c r="W46" s="88" t="n"/>
+      <c r="X46" s="88" t="n"/>
+      <c r="Y46" s="88" t="n"/>
+      <c r="Z46" s="88" t="n"/>
+      <c r="AA46" s="88" t="n"/>
+      <c r="AB46" s="88" t="n"/>
+      <c r="AC46" s="88" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr">
+      <c r="A47" s="88" t="n"/>
+      <c r="B47" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BU2.501010                          </t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="88" t="inlineStr">
         <is>
           <t>4141 Exp St Cst Var</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="E47" s="88" t="n"/>
+      <c r="F47" s="88" t="n"/>
+      <c r="G47" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BUYP   </t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="H47" s="88" t="n"/>
+      <c r="I47" s="88" t="n"/>
+      <c r="J47" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">501010  </t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K47" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="L47" s="88" t="n"/>
+      <c r="M47" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
       </c>
+      <c r="N47" s="88" t="n"/>
+      <c r="O47" s="88" t="n"/>
+      <c r="P47" s="88" t="n"/>
+      <c r="Q47" s="88" t="n"/>
+      <c r="R47" s="88" t="n"/>
+      <c r="S47" s="88" t="n"/>
+      <c r="T47" s="88" t="n"/>
+      <c r="U47" s="88" t="n"/>
+      <c r="V47" s="88" t="n"/>
+      <c r="W47" s="88" t="n"/>
+      <c r="X47" s="88" t="n"/>
+      <c r="Y47" s="88" t="n"/>
+      <c r="Z47" s="88" t="n"/>
+      <c r="AA47" s="88" t="n"/>
+      <c r="AB47" s="88" t="n"/>
+      <c r="AC47" s="88" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr">
+      <c r="A48" s="88" t="n"/>
+      <c r="B48" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BU2.501010                          </t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="88" t="inlineStr">
         <is>
           <t>4220 COGS</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="E48" s="88" t="n"/>
+      <c r="F48" s="88" t="n"/>
+      <c r="G48" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BUYP   </t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="H48" s="88" t="n"/>
+      <c r="I48" s="88" t="n"/>
+      <c r="J48" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">501010  </t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K48" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="L48" s="88" t="n"/>
+      <c r="M48" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
       </c>
+      <c r="N48" s="88" t="n"/>
+      <c r="O48" s="88" t="n"/>
+      <c r="P48" s="88" t="n"/>
+      <c r="Q48" s="88" t="n"/>
+      <c r="R48" s="88" t="n"/>
+      <c r="S48" s="88" t="n"/>
+      <c r="T48" s="88" t="n"/>
+      <c r="U48" s="88" t="n"/>
+      <c r="V48" s="88" t="n"/>
+      <c r="W48" s="88" t="n"/>
+      <c r="X48" s="88" t="n"/>
+      <c r="Y48" s="88" t="n"/>
+      <c r="Z48" s="88" t="n"/>
+      <c r="AA48" s="88" t="n"/>
+      <c r="AB48" s="88" t="n"/>
+      <c r="AC48" s="88" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr">
+      <c r="A49" s="88" t="n"/>
+      <c r="B49" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BU3.401042                          </t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="88" t="inlineStr">
         <is>
           <t>4230 Revenue</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="E49" s="88" t="n"/>
+      <c r="F49" s="88" t="n"/>
+      <c r="G49" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BUYP   </t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="H49" s="88" t="n"/>
+      <c r="I49" s="88" t="n"/>
+      <c r="J49" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">401042  </t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K49" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="L49" s="88" t="n"/>
+      <c r="M49" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
       </c>
+      <c r="N49" s="88" t="n"/>
+      <c r="O49" s="88" t="n"/>
+      <c r="P49" s="88" t="n"/>
+      <c r="Q49" s="88" t="n"/>
+      <c r="R49" s="88" t="n"/>
+      <c r="S49" s="88" t="n"/>
+      <c r="T49" s="88" t="n"/>
+      <c r="U49" s="88" t="n"/>
+      <c r="V49" s="88" t="n"/>
+      <c r="W49" s="88" t="n"/>
+      <c r="X49" s="88" t="n"/>
+      <c r="Y49" s="88" t="n"/>
+      <c r="Z49" s="88" t="n"/>
+      <c r="AA49" s="88" t="n"/>
+      <c r="AB49" s="88" t="n"/>
+      <c r="AC49" s="88" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr">
+      <c r="A50" s="88" t="n"/>
+      <c r="B50" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BU3.409002                          </t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="88" t="inlineStr">
         <is>
           <t>4230 Revenue</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="E50" s="88" t="n"/>
+      <c r="F50" s="88" t="n"/>
+      <c r="G50" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">FT60   </t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="H50" s="88" t="n"/>
+      <c r="I50" s="88" t="n"/>
+      <c r="J50" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">409002  </t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K50" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="L50" s="88" t="n"/>
+      <c r="M50" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
       </c>
+      <c r="N50" s="88" t="n"/>
+      <c r="O50" s="88" t="n"/>
+      <c r="P50" s="88" t="n"/>
+      <c r="Q50" s="88" t="n"/>
+      <c r="R50" s="88" t="n"/>
+      <c r="S50" s="88" t="n"/>
+      <c r="T50" s="88" t="n"/>
+      <c r="U50" s="88" t="n"/>
+      <c r="V50" s="88" t="n"/>
+      <c r="W50" s="88" t="n"/>
+      <c r="X50" s="88" t="n"/>
+      <c r="Y50" s="88" t="n"/>
+      <c r="Z50" s="88" t="n"/>
+      <c r="AA50" s="88" t="n"/>
+      <c r="AB50" s="88" t="n"/>
+      <c r="AC50" s="88" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr">
+      <c r="A51" s="88" t="n"/>
+      <c r="B51" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BU2.501010                          </t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="88" t="inlineStr">
         <is>
           <t>4141 Exp St Cst Var</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="E51" s="88" t="n"/>
+      <c r="F51" s="88" t="n"/>
+      <c r="G51" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SWIT   </t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="H51" s="88" t="n"/>
+      <c r="I51" s="88" t="n"/>
+      <c r="J51" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">501010  </t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K51" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="L51" s="88" t="n"/>
+      <c r="M51" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
       </c>
+      <c r="N51" s="88" t="n"/>
+      <c r="O51" s="88" t="n"/>
+      <c r="P51" s="88" t="n"/>
+      <c r="Q51" s="88" t="n"/>
+      <c r="R51" s="88" t="n"/>
+      <c r="S51" s="88" t="n"/>
+      <c r="T51" s="88" t="n"/>
+      <c r="U51" s="88" t="n"/>
+      <c r="V51" s="88" t="n"/>
+      <c r="W51" s="88" t="n"/>
+      <c r="X51" s="88" t="n"/>
+      <c r="Y51" s="88" t="n"/>
+      <c r="Z51" s="88" t="n"/>
+      <c r="AA51" s="88" t="n"/>
+      <c r="AB51" s="88" t="n"/>
+      <c r="AC51" s="88" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr">
+      <c r="A52" s="88" t="n"/>
+      <c r="B52" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BU2.501010                          </t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="88" t="inlineStr">
         <is>
           <t>4220 COGS</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="E52" s="88" t="n"/>
+      <c r="F52" s="88" t="n"/>
+      <c r="G52" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SWIT   </t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="H52" s="88" t="n"/>
+      <c r="I52" s="88" t="n"/>
+      <c r="J52" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">501010  </t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K52" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="L52" s="88" t="n"/>
+      <c r="M52" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
       </c>
+      <c r="N52" s="88" t="n"/>
+      <c r="O52" s="88" t="n"/>
+      <c r="P52" s="88" t="n"/>
+      <c r="Q52" s="88" t="n"/>
+      <c r="R52" s="88" t="n"/>
+      <c r="S52" s="88" t="n"/>
+      <c r="T52" s="88" t="n"/>
+      <c r="U52" s="88" t="n"/>
+      <c r="V52" s="88" t="n"/>
+      <c r="W52" s="88" t="n"/>
+      <c r="X52" s="88" t="n"/>
+      <c r="Y52" s="88" t="n"/>
+      <c r="Z52" s="88" t="n"/>
+      <c r="AA52" s="88" t="n"/>
+      <c r="AB52" s="88" t="n"/>
+      <c r="AC52" s="88" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr">
+      <c r="A53" s="88" t="n"/>
+      <c r="B53" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">BU3.401012                          </t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="88" t="inlineStr">
         <is>
           <t>4230 Revenue</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">00010  </t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="E53" s="88" t="n"/>
+      <c r="F53" s="88" t="n"/>
+      <c r="G53" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SWIT   </t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="H53" s="88" t="n"/>
+      <c r="I53" s="88" t="n"/>
+      <c r="J53" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">401012  </t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K53" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">SO     </t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="L53" s="88" t="n"/>
+      <c r="M53" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
       </c>
+      <c r="N53" s="88" t="n"/>
+      <c r="O53" s="88" t="n"/>
+      <c r="P53" s="88" t="n"/>
+      <c r="Q53" s="88" t="n"/>
+      <c r="R53" s="88" t="n"/>
+      <c r="S53" s="88" t="n"/>
+      <c r="T53" s="88" t="n"/>
+      <c r="U53" s="88" t="n"/>
+      <c r="V53" s="88" t="n"/>
+      <c r="W53" s="88" t="n"/>
+      <c r="X53" s="88" t="n"/>
+      <c r="Y53" s="88" t="n"/>
+      <c r="Z53" s="88" t="n"/>
+      <c r="AA53" s="88" t="n"/>
+      <c r="AB53" s="88" t="n"/>
+      <c r="AC53" s="88" t="n"/>
     </row>
     <row r="57" ht="24" customHeight="1" s="30"/>
     <row r="59" ht="18" customHeight="1" s="30"/>
@@ -4554,7 +5164,7 @@
     <row r="108" ht="90" customHeight="1" s="30"/>
     <row r="109" ht="75" customHeight="1" s="30"/>
   </sheetData>
-  <autoFilter ref="A2:AC2"/>
+  <autoFilter ref="A2:AC53"/>
   <mergeCells count="1">
     <mergeCell ref="A1:AC1"/>
   </mergeCells>
